--- a/10_Java/学习笔记_包管理_Maven.xlsx
+++ b/10_Java/学习笔记_包管理_Maven.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B095C689-66AD-4D6C-9800-F2F3BABB1088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652B7FBF-0937-4FDD-96CD-18B0A90BD819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概述" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,8 @@
     <sheet name="包管理" sheetId="5" r:id="rId7"/>
     <sheet name="pom.xml" sheetId="6" r:id="rId8"/>
     <sheet name="仓库" sheetId="7" r:id="rId9"/>
-    <sheet name="参考" sheetId="8" r:id="rId10"/>
+    <sheet name="IDE" sheetId="11" r:id="rId10"/>
+    <sheet name="参考" sheetId="8" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="t0" localSheetId="4">配置文件!$B$5</definedName>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="1258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="1259">
   <si>
     <t>该命令执行`dependency`构建阶段中的`copy-dependencies`目标。</t>
   </si>
@@ -2002,9 +2003,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pom.xml配置文件详解</t>
-  </si>
-  <si>
     <t>基础配置</t>
   </si>
   <si>
@@ -2044,21 +2042,6 @@
   </si>
   <si>
     <t>1. maven download  javadoc / sources jar包的时候，需要借助classifier指明要下载那个附属构件</t>
-  </si>
-  <si>
-    <t>引用它的时候就要注明JDK版本，否则maven不知道你到底需要哪一套jar包：</t>
-  </si>
-  <si>
-    <t>构建配置</t>
-  </si>
-  <si>
-    <t>分发配置</t>
-  </si>
-  <si>
-    <t>仓库配置</t>
-  </si>
-  <si>
-    <t>profile配置</t>
   </si>
   <si>
     <t>报表配置</t>
@@ -20524,9 +20507,6 @@
     <t>                    ├─ jquery.min.js</t>
   </si>
   <si>
-    <t>WebJars介绍及使用</t>
-  </si>
-  <si>
     <t>WebJars是一个很神奇的东西，可以让大家以jar包的形式来使用前端的各种框架、组件。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -22797,9 +22777,6 @@
   <si>
     <t>注：分隔符为冒号！！</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Maven pom文件中dependency scope用法</t>
   </si>
   <si>
     <t>依赖范围(Scope)</t>
@@ -25534,12 +25511,79 @@
 &lt;/settings&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>IDEA的Maven配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pom.xml配置文件详解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引用它的时候就要注明JDK版本，否则maven不知道你到底需要哪一套jar包：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>构建配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分发配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仓库配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profile配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Maven pom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="21"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文件中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="21"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>dependency scope</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="21"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用法</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WebJars介绍及使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="110">
+  <fonts count="112">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -26294,6 +26338,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="21"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -26511,7 +26571,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -26847,14 +26907,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -26902,6 +26963,151 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CDE1461-3858-A087-674A-F9D73879D89E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="628650" y="2609850"/>
+          <a:ext cx="11315700" cy="5553075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17D64002-ADED-49D5-336C-FA565D69F3B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="685800" y="8763000"/>
+          <a:ext cx="6943725" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -27394,7 +27600,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -27521,7 +27727,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -27592,7 +27798,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -27754,6 +27960,81 @@
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE7C70B6-93C2-4ADA-92B5-5A996E6A2A44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="781050" y="400050"/>
+          <a:ext cx="8362950" cy="5172075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
         <a:extLst>
           <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
             <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -28043,53 +28324,72 @@
     </row>
     <row r="4" spans="1:3">
       <c r="B4" s="17" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20.25">
       <c r="A7" s="36" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="B8" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="B9" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="C11" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE409DB6-018E-43C4-969A-2AB24792A671}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="20.25">
+      <c r="A1" s="137" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="23.25">
       <c r="A1" s="50" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="B2" s="21" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
@@ -28098,7 +28398,7 @@
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -28109,67 +28409,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="19.5">
       <c r="A1" s="89" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="23.25">
       <c r="B2" s="90" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="18.75">
       <c r="B3" s="91" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18.75">
       <c r="B4" s="92" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="23.25">
       <c r="B5" s="90" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18.75">
       <c r="B6" s="92" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.75">
       <c r="B7" s="92" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18.75">
       <c r="B8" s="92" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="C9" s="21" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="23.25">
       <c r="B10" s="90" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="18.75">
       <c r="B11" s="92" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="18.75">
       <c r="B12" s="92" t="s">
-        <v>1126</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="18.75">
       <c r="B13" s="93" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
@@ -28183,12 +28483,12 @@
     </row>
     <row r="14" spans="1:11" ht="18.75">
       <c r="B14" s="92" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="18.75">
       <c r="B15" s="93" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="C15" s="51"/>
       <c r="D15" s="51"/>
@@ -28202,7 +28502,7 @@
     </row>
     <row r="16" spans="1:11" ht="18.75">
       <c r="B16" s="93" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
@@ -28216,17 +28516,17 @@
     </row>
     <row r="41" spans="2:14" ht="18.75">
       <c r="B41" s="92" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="42" spans="2:14">
       <c r="B42" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="43" spans="2:14" ht="18.75">
       <c r="B43" s="93" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="C43" s="51"/>
       <c r="D43" s="51"/>
@@ -28243,7 +28543,7 @@
     </row>
     <row r="44" spans="2:14" ht="18.75">
       <c r="B44" s="93" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
       <c r="C44" s="51"/>
       <c r="D44" s="51"/>
@@ -28260,7 +28560,7 @@
     </row>
     <row r="45" spans="2:14" ht="18.75">
       <c r="B45" s="93" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="C45" s="51"/>
       <c r="D45" s="51"/>
@@ -28277,7 +28577,7 @@
     </row>
     <row r="47" spans="2:14" ht="18.75">
       <c r="B47" s="93" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="C47" s="51"/>
       <c r="D47" s="51"/>
@@ -28294,7 +28594,7 @@
     </row>
     <row r="48" spans="2:14" ht="18.75">
       <c r="B48" s="93" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="C48" s="51"/>
       <c r="D48" s="51"/>
@@ -28311,7 +28611,7 @@
     </row>
     <row r="49" spans="2:14" ht="18.75">
       <c r="B49" s="93" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="C49" s="51"/>
       <c r="D49" s="51"/>
@@ -28328,7 +28628,7 @@
     </row>
     <row r="50" spans="2:14" ht="18.75">
       <c r="B50" s="93" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="C50" s="51"/>
       <c r="D50" s="51"/>
@@ -28345,7 +28645,7 @@
     </row>
     <row r="51" spans="2:14" ht="18.75">
       <c r="B51" s="93" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C51" s="51"/>
       <c r="D51" s="51"/>
@@ -28362,7 +28662,7 @@
     </row>
     <row r="52" spans="2:14" ht="18.75">
       <c r="B52" s="93" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="C52" s="51"/>
       <c r="D52" s="51"/>
@@ -28379,17 +28679,17 @@
     </row>
     <row r="101" spans="2:14" ht="18.75">
       <c r="B101" s="92" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="102" spans="2:14" ht="18">
       <c r="C102" s="95" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="103" spans="2:14" ht="18.75">
       <c r="B103" s="93" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="C103" s="51"/>
       <c r="D103" s="51"/>
@@ -28406,7 +28706,7 @@
     </row>
     <row r="104" spans="2:14" ht="18.75">
       <c r="B104" s="93" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="C104" s="51"/>
       <c r="D104" s="51"/>
@@ -28423,7 +28723,7 @@
     </row>
     <row r="105" spans="2:14" ht="18.75">
       <c r="B105" s="93" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="C105" s="94"/>
       <c r="D105" s="51"/>
@@ -28440,12 +28740,12 @@
     </row>
     <row r="126" spans="2:14" ht="18.75">
       <c r="B126" s="92" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="127" spans="2:14" ht="18.75">
       <c r="B127" s="93" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="C127" s="51"/>
       <c r="D127" s="51"/>
@@ -28465,12 +28765,12 @@
     </row>
     <row r="131" spans="2:14" ht="18.75">
       <c r="B131" s="92" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="132" spans="2:14" ht="18.75">
       <c r="B132" s="93" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="C132" s="51"/>
       <c r="D132" s="51"/>
@@ -28507,13 +28807,13 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="117" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="115"/>
       <c r="B2" s="22" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -28528,7 +28828,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="22" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -28552,7 +28852,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="117" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -28608,7 +28908,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="B21" s="87" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
@@ -28624,7 +28924,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="B22" s="88" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
@@ -28640,7 +28940,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="B23" s="88" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
@@ -28656,7 +28956,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="B24" s="88" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
@@ -28672,7 +28972,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="B25" s="88" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
@@ -28688,7 +28988,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="B26" s="88" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="51"/>
@@ -28704,7 +29004,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="B27" s="87" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
       <c r="C27" s="51"/>
       <c r="D27" s="51"/>
@@ -28723,7 +29023,7 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="117" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -28733,7 +29033,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="117" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -28743,7 +29043,7 @@
     </row>
     <row r="35" spans="1:2" ht="18.75">
       <c r="A35" s="117" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -28757,7 +29057,7 @@
     </row>
     <row r="38" spans="1:2" ht="18.75">
       <c r="A38" s="119" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -28906,7 +29206,7 @@
     </row>
     <row r="73" spans="2:2">
       <c r="B73" s="55" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="74" spans="2:2">
@@ -29720,12 +30020,12 @@
     </row>
     <row r="224" spans="2:3">
       <c r="B224" s="58" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="225" spans="2:2">
       <c r="B225" s="58" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="226" spans="2:2">
@@ -29861,12 +30161,12 @@
     </row>
     <row r="279" spans="2:2">
       <c r="B279" s="56" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" s="58" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="281" spans="2:2">
@@ -29879,12 +30179,12 @@
     </row>
     <row r="283" spans="2:2">
       <c r="B283" s="56" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" s="58" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="285" spans="2:2">
@@ -29910,12 +30210,12 @@
     </row>
     <row r="290" spans="2:2">
       <c r="B290" s="57" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="291" spans="2:2">
       <c r="B291" s="58" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="292" spans="2:2">
@@ -29938,12 +30238,12 @@
     </row>
     <row r="296" spans="2:2">
       <c r="B296" s="56" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" s="56" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="298" spans="2:2">
@@ -29966,12 +30266,12 @@
     </row>
     <row r="302" spans="2:2">
       <c r="B302" s="57" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" s="57" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="304" spans="2:2">
@@ -30078,12 +30378,12 @@
     </row>
     <row r="320" spans="2:5">
       <c r="B320" s="56" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="321" spans="2:2">
       <c r="B321" s="63" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="322" spans="2:2">
@@ -30091,17 +30391,17 @@
     </row>
     <row r="323" spans="2:2">
       <c r="B323" s="56" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" s="56" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" s="56" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="326" spans="2:2">
@@ -30109,12 +30409,12 @@
     </row>
     <row r="327" spans="2:2">
       <c r="B327" s="56" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" s="63" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="329" spans="2:2">
@@ -30122,12 +30422,12 @@
     </row>
     <row r="330" spans="2:2">
       <c r="B330" s="56" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="331" spans="2:2">
       <c r="B331" s="56" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="332" spans="2:2">
@@ -30177,12 +30477,12 @@
     </row>
     <row r="343" spans="2:5">
       <c r="B343" s="57" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="344" spans="2:5">
       <c r="B344" s="57" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="345" spans="2:5">
@@ -30492,12 +30792,12 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25.5">
       <c r="A1" s="124" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" s="126" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
       <c r="C2" s="127"/>
       <c r="D2" s="127"/>
@@ -30711,17 +31011,17 @@
   <sheetData>
     <row r="1" spans="1:17" ht="30">
       <c r="A1" s="25" t="s">
-        <v>292</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="B2" s="26" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="B3" s="34" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -30729,17 +31029,17 @@
     </row>
     <row r="5" spans="1:17" ht="17.25">
       <c r="B5" s="35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="B6" s="26" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15">
       <c r="B7" s="28" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C7" s="29"/>
       <c r="D7" s="29"/>
@@ -30759,7 +31059,7 @@
     </row>
     <row r="8" spans="1:17" ht="15">
       <c r="B8" s="30" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C8" s="29"/>
       <c r="D8" s="29"/>
@@ -30797,7 +31097,7 @@
     </row>
     <row r="10" spans="1:17" ht="15">
       <c r="B10" s="66" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C10" s="29"/>
       <c r="D10" s="29"/>
@@ -30817,7 +31117,7 @@
     </row>
     <row r="11" spans="1:17" ht="15">
       <c r="B11" s="67" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C11" s="29"/>
       <c r="D11" s="29"/>
@@ -30855,7 +31155,7 @@
     </row>
     <row r="13" spans="1:17" ht="15">
       <c r="B13" s="66" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C13" s="68"/>
       <c r="D13" s="29"/>
@@ -30875,7 +31175,7 @@
     </row>
     <row r="14" spans="1:17" ht="15">
       <c r="B14" s="67" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C14" s="68"/>
       <c r="D14" s="29"/>
@@ -30895,7 +31195,7 @@
     </row>
     <row r="15" spans="1:17" ht="15">
       <c r="B15" s="66" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="29"/>
@@ -30915,7 +31215,7 @@
     </row>
     <row r="16" spans="1:17" ht="15">
       <c r="B16" s="67" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C16" s="68"/>
       <c r="D16" s="29"/>
@@ -30935,7 +31235,7 @@
     </row>
     <row r="17" spans="2:17" ht="15">
       <c r="B17" s="66" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C17" s="68"/>
       <c r="D17" s="29"/>
@@ -30955,7 +31255,7 @@
     </row>
     <row r="18" spans="2:17" ht="15">
       <c r="B18" s="67" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C18" s="68"/>
       <c r="D18" s="29"/>
@@ -30975,7 +31275,7 @@
     </row>
     <row r="19" spans="2:17" ht="15">
       <c r="B19" s="66" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C19" s="68"/>
       <c r="D19" s="29"/>
@@ -30995,7 +31295,7 @@
     </row>
     <row r="20" spans="2:17" ht="15">
       <c r="B20" s="67" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C20" s="68"/>
       <c r="D20" s="29"/>
@@ -31033,7 +31333,7 @@
     </row>
     <row r="22" spans="2:17" ht="15">
       <c r="B22" s="66" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C22" s="29"/>
       <c r="D22" s="29"/>
@@ -31053,7 +31353,7 @@
     </row>
     <row r="23" spans="2:17" ht="15">
       <c r="B23" s="67" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C23" s="29"/>
       <c r="D23" s="29"/>
@@ -31091,7 +31391,7 @@
     </row>
     <row r="25" spans="2:17" ht="15">
       <c r="B25" s="32" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
@@ -31111,7 +31411,7 @@
     </row>
     <row r="26" spans="2:17" ht="15">
       <c r="B26" s="28" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C26" s="29"/>
       <c r="D26" s="29"/>
@@ -31149,7 +31449,7 @@
     </row>
     <row r="28" spans="2:17" ht="15">
       <c r="B28" s="66" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C28" s="68"/>
       <c r="D28" s="29"/>
@@ -31169,7 +31469,7 @@
     </row>
     <row r="29" spans="2:17" ht="15">
       <c r="B29" s="67" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C29" s="68"/>
       <c r="D29" s="29"/>
@@ -31207,7 +31507,7 @@
     </row>
     <row r="31" spans="2:17" ht="15">
       <c r="B31" s="70" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C31" s="71"/>
       <c r="D31" s="29"/>
@@ -31227,7 +31527,7 @@
     </row>
     <row r="32" spans="2:17" ht="15">
       <c r="B32" s="70" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C32" s="71"/>
       <c r="D32" s="29"/>
@@ -31247,7 +31547,7 @@
     </row>
     <row r="33" spans="2:17" ht="15">
       <c r="B33" s="72" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C33" s="71"/>
       <c r="D33" s="29"/>
@@ -31267,7 +31567,7 @@
     </row>
     <row r="34" spans="2:17" ht="15">
       <c r="B34" s="72" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C34" s="71"/>
       <c r="D34" s="29"/>
@@ -31287,7 +31587,7 @@
     </row>
     <row r="35" spans="2:17" ht="15">
       <c r="B35" s="72" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C35" s="71"/>
       <c r="D35" s="29"/>
@@ -31325,7 +31625,7 @@
     </row>
     <row r="37" spans="2:17" ht="15">
       <c r="B37" s="70" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C37" s="71"/>
       <c r="D37" s="29"/>
@@ -31345,7 +31645,7 @@
     </row>
     <row r="38" spans="2:17" ht="15">
       <c r="B38" s="70" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C38" s="71"/>
       <c r="D38" s="29"/>
@@ -31365,7 +31665,7 @@
     </row>
     <row r="39" spans="2:17" ht="15">
       <c r="B39" s="72" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C39" s="71"/>
       <c r="D39" s="29"/>
@@ -31403,7 +31703,7 @@
     </row>
     <row r="41" spans="2:17" ht="15">
       <c r="B41" s="70" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C41" s="71"/>
       <c r="D41" s="29"/>
@@ -31423,7 +31723,7 @@
     </row>
     <row r="42" spans="2:17" ht="15">
       <c r="B42" s="72" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C42" s="71"/>
       <c r="D42" s="29"/>
@@ -31461,7 +31761,7 @@
     </row>
     <row r="44" spans="2:17" ht="15">
       <c r="B44" s="70" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C44" s="71"/>
       <c r="D44" s="29"/>
@@ -31481,7 +31781,7 @@
     </row>
     <row r="45" spans="2:17" ht="15">
       <c r="B45" s="72" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C45" s="71"/>
       <c r="D45" s="29"/>
@@ -31501,7 +31801,7 @@
     </row>
     <row r="46" spans="2:17" ht="15">
       <c r="B46" s="74" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C46" s="75"/>
       <c r="D46" s="29"/>
@@ -31521,7 +31821,7 @@
     </row>
     <row r="47" spans="2:17" ht="15">
       <c r="B47" s="76" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C47" s="77"/>
       <c r="D47" s="29"/>
@@ -31541,7 +31841,7 @@
     </row>
     <row r="48" spans="2:17" ht="15">
       <c r="B48" s="76" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C48" s="77"/>
       <c r="D48" s="29"/>
@@ -31561,7 +31861,7 @@
     </row>
     <row r="49" spans="2:17" ht="15">
       <c r="B49" s="74" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C49" s="75"/>
       <c r="D49" s="29"/>
@@ -31581,7 +31881,7 @@
     </row>
     <row r="50" spans="2:17" ht="15">
       <c r="B50" s="72" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C50" s="71"/>
       <c r="D50" s="29"/>
@@ -31619,7 +31919,7 @@
     </row>
     <row r="52" spans="2:17" ht="15">
       <c r="B52" s="67" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C52" s="68"/>
       <c r="D52" s="29"/>
@@ -31657,7 +31957,7 @@
     </row>
     <row r="54" spans="2:17" ht="15">
       <c r="B54" s="28" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C54" s="29"/>
       <c r="D54" s="29"/>
@@ -31695,7 +31995,7 @@
     </row>
     <row r="56" spans="2:17" ht="15">
       <c r="B56" s="32" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C56" s="29"/>
       <c r="D56" s="29"/>
@@ -31715,7 +32015,7 @@
     </row>
     <row r="57" spans="2:17" ht="15">
       <c r="B57" s="28" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C57" s="29"/>
       <c r="D57" s="29"/>
@@ -31735,7 +32035,7 @@
     </row>
     <row r="58" spans="2:17" ht="15">
       <c r="B58" s="67" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C58" s="29"/>
       <c r="D58" s="29"/>
@@ -31755,7 +32055,7 @@
     </row>
     <row r="59" spans="2:17" ht="15">
       <c r="B59" s="67" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C59" s="29"/>
       <c r="D59" s="29"/>
@@ -31775,7 +32075,7 @@
     </row>
     <row r="60" spans="2:17" ht="15">
       <c r="B60" s="67" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C60" s="29"/>
       <c r="D60" s="29"/>
@@ -31795,7 +32095,7 @@
     </row>
     <row r="61" spans="2:17" ht="15">
       <c r="B61" s="28" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C61" s="29"/>
       <c r="D61" s="29"/>
@@ -31833,7 +32133,7 @@
     </row>
     <row r="63" spans="2:17" ht="15">
       <c r="B63" s="30" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C63" s="29"/>
       <c r="D63" s="29"/>
@@ -31853,7 +32153,7 @@
     </row>
     <row r="64" spans="2:17" ht="15">
       <c r="B64" s="28" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C64" s="29"/>
       <c r="D64" s="29"/>
@@ -31876,12 +32176,12 @@
     </row>
     <row r="66" spans="2:2">
       <c r="B66" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="68" spans="2:2">
@@ -31889,32 +32189,32 @@
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="26" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" s="26" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" s="26" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" s="26" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" s="26" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="76" spans="2:2">
@@ -31988,7 +32288,7 @@
     </row>
     <row r="99" spans="2:13">
       <c r="B99" s="26" t="s">
-        <v>299</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="100" spans="2:13">
@@ -31996,7 +32296,7 @@
     </row>
     <row r="101" spans="2:13" ht="15">
       <c r="B101" s="28" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C101" s="29"/>
       <c r="D101" s="29"/>
@@ -32004,7 +32304,7 @@
     </row>
     <row r="102" spans="2:13" ht="15">
       <c r="B102" s="67" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C102" s="29"/>
       <c r="D102" s="29"/>
@@ -32012,7 +32312,7 @@
     </row>
     <row r="103" spans="2:13" ht="15">
       <c r="B103" s="67" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C103" s="29"/>
       <c r="D103" s="29"/>
@@ -32020,7 +32320,7 @@
     </row>
     <row r="104" spans="2:13" ht="15">
       <c r="B104" s="67" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C104" s="29"/>
       <c r="D104" s="29"/>
@@ -32028,7 +32328,7 @@
     </row>
     <row r="105" spans="2:13" ht="15">
       <c r="B105" s="67" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C105" s="29"/>
       <c r="D105" s="29"/>
@@ -32036,7 +32336,7 @@
     </row>
     <row r="106" spans="2:13" ht="15">
       <c r="B106" s="28" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C106" s="29"/>
       <c r="D106" s="29"/>
@@ -32047,12 +32347,12 @@
     </row>
     <row r="108" spans="2:13" ht="17.25">
       <c r="B108" s="35" t="s">
-        <v>300</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="110" spans="2:13" ht="15">
       <c r="B110" s="28" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C110" s="29"/>
       <c r="D110" s="29"/>
@@ -32068,7 +32368,7 @@
     </row>
     <row r="111" spans="2:13" ht="15">
       <c r="B111" s="66" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C111" s="29"/>
       <c r="D111" s="29"/>
@@ -32084,7 +32384,7 @@
     </row>
     <row r="112" spans="2:13" ht="15">
       <c r="B112" s="67" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C112" s="29"/>
       <c r="D112" s="29"/>
@@ -32100,7 +32400,7 @@
     </row>
     <row r="113" spans="2:13" ht="15">
       <c r="B113" s="66" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C113" s="29"/>
       <c r="D113" s="29"/>
@@ -32116,7 +32416,7 @@
     </row>
     <row r="114" spans="2:13" ht="15">
       <c r="B114" s="67" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C114" s="29"/>
       <c r="D114" s="29"/>
@@ -32132,7 +32432,7 @@
     </row>
     <row r="115" spans="2:13" ht="15">
       <c r="B115" s="66" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C115" s="29"/>
       <c r="D115" s="29"/>
@@ -32148,7 +32448,7 @@
     </row>
     <row r="116" spans="2:13" ht="15">
       <c r="B116" s="66" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C116" s="29"/>
       <c r="D116" s="29"/>
@@ -32164,7 +32464,7 @@
     </row>
     <row r="117" spans="2:13" ht="15">
       <c r="B117" s="67" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C117" s="29"/>
       <c r="D117" s="29"/>
@@ -32194,7 +32494,7 @@
     </row>
     <row r="119" spans="2:13" ht="15">
       <c r="B119" s="66" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C119" s="29"/>
       <c r="D119" s="29"/>
@@ -32210,7 +32510,7 @@
     </row>
     <row r="120" spans="2:13" ht="15">
       <c r="B120" s="66" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C120" s="29"/>
       <c r="D120" s="29"/>
@@ -32226,7 +32526,7 @@
     </row>
     <row r="121" spans="2:13" ht="15">
       <c r="B121" s="67" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C121" s="29"/>
       <c r="D121" s="29"/>
@@ -32242,7 +32542,7 @@
     </row>
     <row r="122" spans="2:13" ht="15">
       <c r="B122" s="72" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C122" s="29"/>
       <c r="D122" s="29"/>
@@ -32258,7 +32558,7 @@
     </row>
     <row r="123" spans="2:13" ht="15">
       <c r="B123" s="67" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C123" s="29"/>
       <c r="D123" s="29"/>
@@ -32288,7 +32588,7 @@
     </row>
     <row r="125" spans="2:13" ht="15">
       <c r="B125" s="66" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C125" s="29"/>
       <c r="D125" s="29"/>
@@ -32304,7 +32604,7 @@
     </row>
     <row r="126" spans="2:13" ht="15">
       <c r="B126" s="67" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C126" s="29"/>
       <c r="D126" s="29"/>
@@ -32320,7 +32620,7 @@
     </row>
     <row r="127" spans="2:13" ht="15">
       <c r="B127" s="72" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C127" s="68"/>
       <c r="D127" s="29"/>
@@ -32336,7 +32636,7 @@
     </row>
     <row r="128" spans="2:13" ht="15">
       <c r="B128" s="79" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C128" s="71"/>
       <c r="D128" s="29"/>
@@ -32352,7 +32652,7 @@
     </row>
     <row r="129" spans="2:13" ht="15">
       <c r="B129" s="79" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C129" s="71"/>
       <c r="D129" s="29"/>
@@ -32368,7 +32668,7 @@
     </row>
     <row r="130" spans="2:13" ht="15">
       <c r="B130" s="79" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C130" s="71"/>
       <c r="D130" s="29"/>
@@ -32384,7 +32684,7 @@
     </row>
     <row r="131" spans="2:13" ht="15">
       <c r="B131" s="74" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C131" s="71"/>
       <c r="D131" s="29"/>
@@ -32400,7 +32700,7 @@
     </row>
     <row r="132" spans="2:13" ht="15">
       <c r="B132" s="79" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C132" s="71"/>
       <c r="D132" s="29"/>
@@ -32416,7 +32716,7 @@
     </row>
     <row r="133" spans="2:13" ht="15">
       <c r="B133" s="74" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C133" s="71"/>
       <c r="D133" s="29"/>
@@ -32432,7 +32732,7 @@
     </row>
     <row r="134" spans="2:13" ht="15">
       <c r="B134" s="79" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C134" s="71"/>
       <c r="D134" s="29"/>
@@ -32448,7 +32748,7 @@
     </row>
     <row r="135" spans="2:13" ht="15">
       <c r="B135" s="74" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C135" s="71"/>
       <c r="D135" s="29"/>
@@ -32478,7 +32778,7 @@
     </row>
     <row r="137" spans="2:13" ht="15">
       <c r="B137" s="79" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C137" s="71"/>
       <c r="D137" s="29"/>
@@ -32494,7 +32794,7 @@
     </row>
     <row r="138" spans="2:13" ht="15">
       <c r="B138" s="74" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C138" s="71"/>
       <c r="D138" s="29"/>
@@ -32510,7 +32810,7 @@
     </row>
     <row r="139" spans="2:13" ht="15">
       <c r="B139" s="76" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C139" s="71"/>
       <c r="D139" s="29"/>
@@ -32526,7 +32826,7 @@
     </row>
     <row r="140" spans="2:13" ht="15">
       <c r="B140" s="76" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C140" s="71"/>
       <c r="D140" s="29"/>
@@ -32542,7 +32842,7 @@
     </row>
     <row r="141" spans="2:13" ht="15">
       <c r="B141" s="74" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C141" s="71"/>
       <c r="D141" s="29"/>
@@ -32572,7 +32872,7 @@
     </row>
     <row r="143" spans="2:13" ht="15">
       <c r="B143" s="79" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C143" s="71"/>
       <c r="D143" s="29"/>
@@ -32588,7 +32888,7 @@
     </row>
     <row r="144" spans="2:13" ht="15">
       <c r="B144" s="74" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C144" s="71"/>
       <c r="D144" s="29"/>
@@ -32604,7 +32904,7 @@
     </row>
     <row r="145" spans="2:13" ht="15">
       <c r="B145" s="74" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C145" s="71"/>
       <c r="D145" s="29"/>
@@ -32620,7 +32920,7 @@
     </row>
     <row r="146" spans="2:13" ht="15">
       <c r="B146" s="74" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C146" s="71"/>
       <c r="D146" s="29"/>
@@ -32636,7 +32936,7 @@
     </row>
     <row r="147" spans="2:13" ht="15">
       <c r="B147" s="72" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C147" s="68"/>
       <c r="D147" s="29"/>
@@ -32652,7 +32952,7 @@
     </row>
     <row r="148" spans="2:13" ht="15">
       <c r="B148" s="67" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C148" s="29"/>
       <c r="D148" s="29"/>
@@ -32682,7 +32982,7 @@
     </row>
     <row r="150" spans="2:13" ht="15">
       <c r="B150" s="66" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C150" s="29"/>
       <c r="D150" s="29"/>
@@ -32698,7 +32998,7 @@
     </row>
     <row r="151" spans="2:13" ht="15">
       <c r="B151" s="67" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C151" s="29"/>
       <c r="D151" s="29"/>
@@ -32714,7 +33014,7 @@
     </row>
     <row r="152" spans="2:13" ht="15">
       <c r="B152" s="72" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C152" s="29"/>
       <c r="D152" s="29"/>
@@ -32730,7 +33030,7 @@
     </row>
     <row r="153" spans="2:13" ht="15">
       <c r="B153" s="74" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C153" s="68"/>
       <c r="D153" s="29"/>
@@ -32746,7 +33046,7 @@
     </row>
     <row r="154" spans="2:13" ht="15">
       <c r="B154" s="74" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C154" s="68"/>
       <c r="D154" s="29"/>
@@ -32762,7 +33062,7 @@
     </row>
     <row r="155" spans="2:13" ht="15">
       <c r="B155" s="74" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C155" s="68"/>
       <c r="D155" s="29"/>
@@ -32778,7 +33078,7 @@
     </row>
     <row r="156" spans="2:13" ht="15">
       <c r="B156" s="74" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C156" s="68"/>
       <c r="D156" s="29"/>
@@ -32794,7 +33094,7 @@
     </row>
     <row r="157" spans="2:13" ht="15">
       <c r="B157" s="74" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C157" s="68"/>
       <c r="D157" s="29"/>
@@ -32810,7 +33110,7 @@
     </row>
     <row r="158" spans="2:13" ht="15">
       <c r="B158" s="72" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C158" s="29"/>
       <c r="D158" s="29"/>
@@ -32826,7 +33126,7 @@
     </row>
     <row r="159" spans="2:13" ht="15">
       <c r="B159" s="67" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C159" s="29"/>
       <c r="D159" s="29"/>
@@ -32856,7 +33156,7 @@
     </row>
     <row r="161" spans="2:13" ht="15">
       <c r="B161" s="66" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C161" s="29"/>
       <c r="D161" s="29"/>
@@ -32872,7 +33172,7 @@
     </row>
     <row r="162" spans="2:13" ht="15">
       <c r="B162" s="67" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C162" s="29"/>
       <c r="D162" s="29"/>
@@ -32888,7 +33188,7 @@
     </row>
     <row r="163" spans="2:13" ht="15">
       <c r="B163" s="66" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C163" s="29"/>
       <c r="D163" s="29"/>
@@ -32904,7 +33204,7 @@
     </row>
     <row r="164" spans="2:13" ht="15">
       <c r="B164" s="78" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C164" s="29"/>
       <c r="D164" s="29"/>
@@ -32920,7 +33220,7 @@
     </row>
     <row r="165" spans="2:13" ht="15">
       <c r="B165" s="67" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C165" s="29"/>
       <c r="D165" s="29"/>
@@ -32936,7 +33236,7 @@
     </row>
     <row r="166" spans="2:13" ht="15">
       <c r="B166" s="66" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C166" s="29"/>
       <c r="D166" s="29"/>
@@ -32952,7 +33252,7 @@
     </row>
     <row r="167" spans="2:13" ht="15">
       <c r="B167" s="67" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C167" s="29"/>
       <c r="D167" s="29"/>
@@ -32968,7 +33268,7 @@
     </row>
     <row r="168" spans="2:13" ht="15">
       <c r="B168" s="66" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C168" s="29"/>
       <c r="D168" s="29"/>
@@ -32984,7 +33284,7 @@
     </row>
     <row r="169" spans="2:13" ht="15">
       <c r="B169" s="67" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C169" s="29"/>
       <c r="D169" s="29"/>
@@ -33000,7 +33300,7 @@
     </row>
     <row r="170" spans="2:13" ht="15">
       <c r="B170" s="66" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C170" s="29"/>
       <c r="D170" s="29"/>
@@ -33016,7 +33316,7 @@
     </row>
     <row r="171" spans="2:13" ht="15">
       <c r="B171" s="67" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C171" s="29"/>
       <c r="D171" s="29"/>
@@ -33032,7 +33332,7 @@
     </row>
     <row r="172" spans="2:13" ht="15">
       <c r="B172" s="67" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C172" s="29"/>
       <c r="D172" s="29"/>
@@ -33048,7 +33348,7 @@
     </row>
     <row r="173" spans="2:13" ht="15">
       <c r="B173" s="66" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C173" s="29"/>
       <c r="D173" s="29"/>
@@ -33064,7 +33364,7 @@
     </row>
     <row r="174" spans="2:13" ht="15">
       <c r="B174" s="66" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C174" s="29"/>
       <c r="D174" s="29"/>
@@ -33080,7 +33380,7 @@
     </row>
     <row r="175" spans="2:13" ht="15">
       <c r="B175" s="66" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C175" s="29"/>
       <c r="D175" s="29"/>
@@ -33110,7 +33410,7 @@
     </row>
     <row r="177" spans="2:13" ht="15">
       <c r="B177" s="67" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C177" s="29"/>
       <c r="D177" s="29"/>
@@ -33126,7 +33426,7 @@
     </row>
     <row r="178" spans="2:13" ht="15">
       <c r="B178" s="70" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C178" s="68"/>
       <c r="D178" s="29"/>
@@ -33142,7 +33442,7 @@
     </row>
     <row r="179" spans="2:13" ht="15">
       <c r="B179" s="70" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C179" s="68"/>
       <c r="D179" s="29"/>
@@ -33158,7 +33458,7 @@
     </row>
     <row r="180" spans="2:13" ht="15">
       <c r="B180" s="70" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C180" s="68"/>
       <c r="D180" s="29"/>
@@ -33174,7 +33474,7 @@
     </row>
     <row r="181" spans="2:13" ht="15">
       <c r="B181" s="70" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C181" s="68"/>
       <c r="D181" s="29"/>
@@ -33190,7 +33490,7 @@
     </row>
     <row r="182" spans="2:13" ht="15">
       <c r="B182" s="70" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C182" s="68"/>
       <c r="D182" s="29"/>
@@ -33206,7 +33506,7 @@
     </row>
     <row r="183" spans="2:13" ht="15">
       <c r="B183" s="72" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C183" s="68"/>
       <c r="D183" s="29"/>
@@ -33222,7 +33522,7 @@
     </row>
     <row r="184" spans="2:13" ht="15">
       <c r="B184" s="74" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C184" s="68"/>
       <c r="D184" s="29"/>
@@ -33238,7 +33538,7 @@
     </row>
     <row r="185" spans="2:13" ht="15">
       <c r="B185" s="74" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C185" s="68"/>
       <c r="D185" s="29"/>
@@ -33254,7 +33554,7 @@
     </row>
     <row r="186" spans="2:13" ht="15">
       <c r="B186" s="74" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C186" s="68"/>
       <c r="D186" s="29"/>
@@ -33270,7 +33570,7 @@
     </row>
     <row r="187" spans="2:13" ht="15">
       <c r="B187" s="72" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C187" s="68"/>
       <c r="D187" s="29"/>
@@ -33286,7 +33586,7 @@
     </row>
     <row r="188" spans="2:13" ht="15">
       <c r="B188" s="67" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C188" s="29"/>
       <c r="D188" s="29"/>
@@ -33316,7 +33616,7 @@
     </row>
     <row r="190" spans="2:13" ht="15">
       <c r="B190" s="66" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C190" s="29"/>
       <c r="D190" s="29"/>
@@ -33332,7 +33632,7 @@
     </row>
     <row r="191" spans="2:13" ht="15">
       <c r="B191" s="67" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C191" s="29"/>
       <c r="D191" s="29"/>
@@ -33348,7 +33648,7 @@
     </row>
     <row r="192" spans="2:13" ht="15">
       <c r="B192" s="72" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C192" s="29"/>
       <c r="D192" s="29"/>
@@ -33364,7 +33664,7 @@
     </row>
     <row r="193" spans="2:13" ht="15">
       <c r="B193" s="72" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C193" s="29"/>
       <c r="D193" s="29"/>
@@ -33380,7 +33680,7 @@
     </row>
     <row r="194" spans="2:13" ht="15">
       <c r="B194" s="72" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C194" s="29"/>
       <c r="D194" s="29"/>
@@ -33396,7 +33696,7 @@
     </row>
     <row r="195" spans="2:13" ht="15">
       <c r="B195" s="72" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C195" s="29"/>
       <c r="D195" s="29"/>
@@ -33426,7 +33726,7 @@
     </row>
     <row r="197" spans="2:13" ht="15">
       <c r="B197" s="70" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C197" s="29"/>
       <c r="D197" s="29"/>
@@ -33442,7 +33742,7 @@
     </row>
     <row r="198" spans="2:13" ht="15">
       <c r="B198" s="72" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C198" s="29"/>
       <c r="D198" s="29"/>
@@ -33458,7 +33758,7 @@
     </row>
     <row r="199" spans="2:13" ht="15">
       <c r="B199" s="74" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C199" s="29"/>
       <c r="D199" s="29"/>
@@ -33474,7 +33774,7 @@
     </row>
     <row r="200" spans="2:13" ht="15">
       <c r="B200" s="80" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C200" s="68"/>
       <c r="D200" s="29"/>
@@ -33490,7 +33790,7 @@
     </row>
     <row r="201" spans="2:13" ht="15">
       <c r="B201" s="76" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C201" s="68"/>
       <c r="D201" s="29"/>
@@ -33506,7 +33806,7 @@
     </row>
     <row r="202" spans="2:13" ht="15">
       <c r="B202" s="80" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C202" s="68"/>
       <c r="D202" s="29"/>
@@ -33522,7 +33822,7 @@
     </row>
     <row r="203" spans="2:13" ht="15">
       <c r="B203" s="76" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C203" s="68"/>
       <c r="D203" s="29"/>
@@ -33538,7 +33838,7 @@
     </row>
     <row r="204" spans="2:13" ht="15">
       <c r="B204" s="80" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C204" s="68"/>
       <c r="D204" s="29"/>
@@ -33554,7 +33854,7 @@
     </row>
     <row r="205" spans="2:13" ht="15">
       <c r="B205" s="76" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C205" s="68"/>
       <c r="D205" s="29"/>
@@ -33570,7 +33870,7 @@
     </row>
     <row r="206" spans="2:13" ht="15">
       <c r="B206" s="81" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C206" s="68"/>
       <c r="D206" s="29"/>
@@ -33586,7 +33886,7 @@
     </row>
     <row r="207" spans="2:13" ht="15">
       <c r="B207" s="76" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C207" s="68"/>
       <c r="D207" s="29"/>
@@ -33602,7 +33902,7 @@
     </row>
     <row r="208" spans="2:13" ht="15">
       <c r="B208" s="80" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C208" s="68"/>
       <c r="D208" s="29"/>
@@ -33618,7 +33918,7 @@
     </row>
     <row r="209" spans="2:13" ht="15">
       <c r="B209" s="76" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C209" s="68"/>
       <c r="D209" s="29"/>
@@ -33634,7 +33934,7 @@
     </row>
     <row r="210" spans="2:13" ht="15">
       <c r="B210" s="74" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C210" s="29"/>
       <c r="D210" s="29"/>
@@ -33650,7 +33950,7 @@
     </row>
     <row r="211" spans="2:13" ht="15">
       <c r="B211" s="72" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C211" s="29"/>
       <c r="D211" s="29"/>
@@ -33680,7 +33980,7 @@
     </row>
     <row r="213" spans="2:13" ht="15">
       <c r="B213" s="70" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C213" s="29"/>
       <c r="D213" s="29"/>
@@ -33696,7 +33996,7 @@
     </row>
     <row r="214" spans="2:13" ht="15">
       <c r="B214" s="72" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C214" s="29"/>
       <c r="D214" s="29"/>
@@ -33712,7 +34012,7 @@
     </row>
     <row r="215" spans="2:13" ht="15">
       <c r="B215" s="74" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C215" s="29"/>
       <c r="D215" s="29"/>
@@ -33728,7 +34028,7 @@
     </row>
     <row r="216" spans="2:13" ht="15">
       <c r="B216" s="74" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C216" s="29"/>
       <c r="D216" s="29"/>
@@ -33744,7 +34044,7 @@
     </row>
     <row r="217" spans="2:13" ht="15">
       <c r="B217" s="74" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C217" s="29"/>
       <c r="D217" s="29"/>
@@ -33760,7 +34060,7 @@
     </row>
     <row r="218" spans="2:13" ht="15">
       <c r="B218" s="72" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C218" s="29"/>
       <c r="D218" s="29"/>
@@ -33790,7 +34090,7 @@
     </row>
     <row r="220" spans="2:13" ht="15">
       <c r="B220" s="70" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C220" s="29"/>
       <c r="D220" s="29"/>
@@ -33806,7 +34106,7 @@
     </row>
     <row r="221" spans="2:13" ht="15">
       <c r="B221" s="70" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C221" s="29"/>
       <c r="D221" s="29"/>
@@ -33822,7 +34122,7 @@
     </row>
     <row r="222" spans="2:13" ht="15">
       <c r="B222" s="72" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C222" s="29"/>
       <c r="D222" s="29"/>
@@ -33852,7 +34152,7 @@
     </row>
     <row r="224" spans="2:13" ht="15">
       <c r="B224" s="70" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C224" s="29"/>
       <c r="D224" s="29"/>
@@ -33868,7 +34168,7 @@
     </row>
     <row r="225" spans="2:13" ht="15">
       <c r="B225" s="72" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C225" s="29"/>
       <c r="D225" s="29"/>
@@ -33884,7 +34184,7 @@
     </row>
     <row r="226" spans="2:13" ht="15">
       <c r="B226" s="74" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C226" s="29"/>
       <c r="D226" s="29"/>
@@ -33900,7 +34200,7 @@
     </row>
     <row r="227" spans="2:13" ht="15">
       <c r="B227" s="72" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C227" s="29"/>
       <c r="D227" s="29"/>
@@ -33930,7 +34230,7 @@
     </row>
     <row r="229" spans="2:13" ht="15">
       <c r="B229" s="70" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C229" s="29"/>
       <c r="D229" s="29"/>
@@ -33946,7 +34246,7 @@
     </row>
     <row r="230" spans="2:13" ht="15">
       <c r="B230" s="72" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C230" s="29"/>
       <c r="D230" s="29"/>
@@ -33962,7 +34262,7 @@
     </row>
     <row r="231" spans="2:13" ht="15">
       <c r="B231" s="72" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C231" s="29"/>
       <c r="D231" s="29"/>
@@ -33978,7 +34278,7 @@
     </row>
     <row r="232" spans="2:13" ht="15">
       <c r="B232" s="67" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C232" s="29"/>
       <c r="D232" s="29"/>
@@ -34008,7 +34308,7 @@
     </row>
     <row r="234" spans="2:13" ht="15">
       <c r="B234" s="66" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C234" s="29"/>
       <c r="D234" s="29"/>
@@ -34024,7 +34324,7 @@
     </row>
     <row r="235" spans="2:13" ht="15">
       <c r="B235" s="66" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C235" s="29"/>
       <c r="D235" s="29"/>
@@ -34040,7 +34340,7 @@
     </row>
     <row r="236" spans="2:13" ht="15">
       <c r="B236" s="66" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C236" s="29"/>
       <c r="D236" s="29"/>
@@ -34056,7 +34356,7 @@
     </row>
     <row r="237" spans="2:13" ht="15">
       <c r="B237" s="67" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C237" s="29"/>
       <c r="D237" s="29"/>
@@ -34072,7 +34372,7 @@
     </row>
     <row r="238" spans="2:13" ht="15">
       <c r="B238" s="67" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C238" s="29"/>
       <c r="D238" s="29"/>
@@ -34088,7 +34388,7 @@
     </row>
     <row r="239" spans="2:13" ht="15">
       <c r="B239" s="67" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C239" s="29"/>
       <c r="D239" s="29"/>
@@ -34104,7 +34404,7 @@
     </row>
     <row r="240" spans="2:13" ht="15">
       <c r="B240" s="28" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C240" s="29"/>
       <c r="D240" s="29"/>
@@ -34123,12 +34423,12 @@
     </row>
     <row r="242" spans="2:14">
       <c r="B242" s="26" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="243" spans="2:14">
       <c r="B243" s="26" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="244" spans="2:14">
@@ -34136,12 +34436,12 @@
     </row>
     <row r="245" spans="2:14" ht="17.25">
       <c r="B245" s="35" t="s">
-        <v>301</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="246" spans="2:14" ht="15">
       <c r="B246" s="32" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C246" s="29"/>
       <c r="D246" s="29"/>
@@ -34158,7 +34458,7 @@
     </row>
     <row r="247" spans="2:14" ht="15">
       <c r="B247" s="32" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C247" s="29"/>
       <c r="D247" s="29"/>
@@ -34175,7 +34475,7 @@
     </row>
     <row r="248" spans="2:14" ht="15">
       <c r="B248" s="28" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C248" s="29"/>
       <c r="D248" s="29"/>
@@ -34192,7 +34492,7 @@
     </row>
     <row r="249" spans="2:14" ht="15">
       <c r="B249" s="66" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C249" s="29"/>
       <c r="D249" s="29"/>
@@ -34209,7 +34509,7 @@
     </row>
     <row r="250" spans="2:14" ht="15">
       <c r="B250" s="67" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C250" s="29"/>
       <c r="D250" s="29"/>
@@ -34226,7 +34526,7 @@
     </row>
     <row r="251" spans="2:14" ht="15">
       <c r="B251" s="70" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C251" s="29"/>
       <c r="D251" s="29"/>
@@ -34243,7 +34543,7 @@
     </row>
     <row r="252" spans="2:14" ht="15">
       <c r="B252" s="70" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C252" s="29"/>
       <c r="D252" s="29"/>
@@ -34260,7 +34560,7 @@
     </row>
     <row r="253" spans="2:14" ht="15">
       <c r="B253" s="72" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C253" s="29"/>
       <c r="D253" s="29"/>
@@ -34277,7 +34577,7 @@
     </row>
     <row r="254" spans="2:14" ht="15">
       <c r="B254" s="72" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C254" s="29"/>
       <c r="D254" s="29"/>
@@ -34294,7 +34594,7 @@
     </row>
     <row r="255" spans="2:14" ht="15">
       <c r="B255" s="72" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C255" s="29"/>
       <c r="D255" s="29"/>
@@ -34311,7 +34611,7 @@
     </row>
     <row r="256" spans="2:14" ht="15">
       <c r="B256" s="72" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C256" s="29"/>
       <c r="D256" s="29"/>
@@ -34328,7 +34628,7 @@
     </row>
     <row r="257" spans="1:14" ht="15">
       <c r="B257" s="72" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C257" s="29"/>
       <c r="D257" s="29"/>
@@ -34345,7 +34645,7 @@
     </row>
     <row r="258" spans="1:14" ht="15">
       <c r="B258" s="67" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C258" s="29"/>
       <c r="D258" s="29"/>
@@ -34377,7 +34677,7 @@
     </row>
     <row r="260" spans="1:14" ht="15">
       <c r="B260" s="66" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C260" s="29"/>
       <c r="D260" s="29"/>
@@ -34394,7 +34694,7 @@
     </row>
     <row r="261" spans="1:14" ht="15">
       <c r="B261" s="67" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C261" s="29"/>
       <c r="D261" s="29"/>
@@ -34412,7 +34712,7 @@
     <row r="262" spans="1:14" ht="15">
       <c r="A262" s="82"/>
       <c r="B262" s="72" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C262" s="68"/>
       <c r="D262" s="29"/>
@@ -34430,7 +34730,7 @@
     <row r="263" spans="1:14" ht="15">
       <c r="A263" s="82"/>
       <c r="B263" s="72" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C263" s="68"/>
       <c r="D263" s="29"/>
@@ -34448,7 +34748,7 @@
     <row r="264" spans="1:14" ht="15">
       <c r="A264" s="82"/>
       <c r="B264" s="72" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C264" s="68"/>
       <c r="D264" s="29"/>
@@ -34466,7 +34766,7 @@
     <row r="265" spans="1:14" ht="15">
       <c r="A265" s="82"/>
       <c r="B265" s="72" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C265" s="68"/>
       <c r="D265" s="29"/>
@@ -34484,7 +34784,7 @@
     <row r="266" spans="1:14" ht="15">
       <c r="A266" s="82"/>
       <c r="B266" s="72" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C266" s="68"/>
       <c r="D266" s="29"/>
@@ -34501,7 +34801,7 @@
     </row>
     <row r="267" spans="1:14" ht="15">
       <c r="B267" s="67" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C267" s="29"/>
       <c r="D267" s="29"/>
@@ -34533,7 +34833,7 @@
     </row>
     <row r="269" spans="1:14" ht="15">
       <c r="B269" s="66" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C269" s="29"/>
       <c r="D269" s="29"/>
@@ -34550,7 +34850,7 @@
     </row>
     <row r="270" spans="1:14" ht="15">
       <c r="B270" s="67" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C270" s="29"/>
       <c r="D270" s="29"/>
@@ -34567,7 +34867,7 @@
     </row>
     <row r="271" spans="1:14" ht="15">
       <c r="B271" s="70" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C271" s="29"/>
       <c r="D271" s="29"/>
@@ -34584,7 +34884,7 @@
     </row>
     <row r="272" spans="1:14" ht="15">
       <c r="B272" s="72" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C272" s="29"/>
       <c r="D272" s="29"/>
@@ -34601,7 +34901,7 @@
     </row>
     <row r="273" spans="2:14" ht="15">
       <c r="B273" s="70" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C273" s="29"/>
       <c r="D273" s="29"/>
@@ -34618,7 +34918,7 @@
     </row>
     <row r="274" spans="2:14" ht="15">
       <c r="B274" s="72" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C274" s="29"/>
       <c r="D274" s="29"/>
@@ -34635,7 +34935,7 @@
     </row>
     <row r="275" spans="2:14" ht="15">
       <c r="B275" s="70" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C275" s="29"/>
       <c r="D275" s="29"/>
@@ -34652,7 +34952,7 @@
     </row>
     <row r="276" spans="2:14" ht="15">
       <c r="B276" s="72" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C276" s="29"/>
       <c r="D276" s="29"/>
@@ -34669,7 +34969,7 @@
     </row>
     <row r="277" spans="2:14" ht="15">
       <c r="B277" s="67" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C277" s="29"/>
       <c r="D277" s="29"/>
@@ -34701,7 +35001,7 @@
     </row>
     <row r="279" spans="2:14" ht="15">
       <c r="B279" s="66" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C279" s="29"/>
       <c r="D279" s="29"/>
@@ -34718,7 +35018,7 @@
     </row>
     <row r="280" spans="2:14" ht="15">
       <c r="B280" s="66" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C280" s="29"/>
       <c r="D280" s="29"/>
@@ -34735,7 +35035,7 @@
     </row>
     <row r="281" spans="2:14" ht="15">
       <c r="B281" s="67" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C281" s="29"/>
       <c r="D281" s="29"/>
@@ -34767,7 +35067,7 @@
     </row>
     <row r="283" spans="2:14" ht="15">
       <c r="B283" s="66" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C283" s="29"/>
       <c r="D283" s="29"/>
@@ -34784,7 +35084,7 @@
     </row>
     <row r="284" spans="2:14" ht="15">
       <c r="B284" s="67" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C284" s="29"/>
       <c r="D284" s="29"/>
@@ -34801,7 +35101,7 @@
     </row>
     <row r="285" spans="2:14" ht="15">
       <c r="B285" s="70" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C285" s="29"/>
       <c r="D285" s="29"/>
@@ -34818,7 +35118,7 @@
     </row>
     <row r="286" spans="2:14" ht="15">
       <c r="B286" s="72" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C286" s="29"/>
       <c r="D286" s="29"/>
@@ -34835,7 +35135,7 @@
     </row>
     <row r="287" spans="2:14" ht="15">
       <c r="B287" s="70" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C287" s="29"/>
       <c r="D287" s="29"/>
@@ -34852,7 +35152,7 @@
     </row>
     <row r="288" spans="2:14" ht="15">
       <c r="B288" s="72" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C288" s="29"/>
       <c r="D288" s="29"/>
@@ -34869,7 +35169,7 @@
     </row>
     <row r="289" spans="2:14" ht="15">
       <c r="B289" s="70" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C289" s="29"/>
       <c r="D289" s="29"/>
@@ -34886,7 +35186,7 @@
     </row>
     <row r="290" spans="2:14" ht="15">
       <c r="B290" s="72" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C290" s="29"/>
       <c r="D290" s="29"/>
@@ -34903,7 +35203,7 @@
     </row>
     <row r="291" spans="2:14" ht="15">
       <c r="B291" s="70" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="C291" s="29"/>
       <c r="D291" s="29"/>
@@ -34920,7 +35220,7 @@
     </row>
     <row r="292" spans="2:14" ht="15">
       <c r="B292" s="72" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="C292" s="29"/>
       <c r="D292" s="29"/>
@@ -34937,7 +35237,7 @@
     </row>
     <row r="293" spans="2:14" ht="15">
       <c r="B293" s="67" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C293" s="29"/>
       <c r="D293" s="29"/>
@@ -34969,7 +35269,7 @@
     </row>
     <row r="295" spans="2:14" ht="15">
       <c r="B295" s="66" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C295" s="29"/>
       <c r="D295" s="29"/>
@@ -34986,7 +35286,7 @@
     </row>
     <row r="296" spans="2:14" ht="15">
       <c r="B296" s="66" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C296" s="29"/>
       <c r="D296" s="29"/>
@@ -35003,7 +35303,7 @@
     </row>
     <row r="297" spans="2:14" ht="15">
       <c r="B297" s="66" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C297" s="29"/>
       <c r="D297" s="29"/>
@@ -35020,7 +35320,7 @@
     </row>
     <row r="298" spans="2:14" ht="15">
       <c r="B298" s="67" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C298" s="29"/>
       <c r="D298" s="29"/>
@@ -35037,7 +35337,7 @@
     </row>
     <row r="299" spans="2:14" ht="15">
       <c r="B299" s="28" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C299" s="29"/>
       <c r="D299" s="29"/>
@@ -35054,7 +35354,7 @@
     </row>
     <row r="301" spans="2:14" ht="17.25">
       <c r="B301" s="35" t="s">
-        <v>302</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="302" spans="2:14">
@@ -35062,7 +35362,7 @@
     </row>
     <row r="303" spans="2:14" ht="15">
       <c r="B303" s="32" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C303" s="29"/>
       <c r="D303" s="29"/>
@@ -35075,7 +35375,7 @@
     </row>
     <row r="304" spans="2:14" ht="15">
       <c r="B304" s="28" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C304" s="29"/>
       <c r="D304" s="29"/>
@@ -35088,7 +35388,7 @@
     </row>
     <row r="305" spans="2:10" ht="15">
       <c r="B305" s="66" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="C305" s="29"/>
       <c r="D305" s="29"/>
@@ -35101,7 +35401,7 @@
     </row>
     <row r="306" spans="2:10" ht="15">
       <c r="B306" s="67" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C306" s="29"/>
       <c r="D306" s="29"/>
@@ -35114,7 +35414,7 @@
     </row>
     <row r="307" spans="2:10" ht="15">
       <c r="B307" s="70" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C307" s="68"/>
       <c r="D307" s="29"/>
@@ -35127,7 +35427,7 @@
     </row>
     <row r="308" spans="2:10" ht="15">
       <c r="B308" s="72" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C308" s="68"/>
       <c r="D308" s="29"/>
@@ -35140,7 +35440,7 @@
     </row>
     <row r="309" spans="2:10" ht="15">
       <c r="B309" s="79" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C309" s="71"/>
       <c r="D309" s="29"/>
@@ -35153,7 +35453,7 @@
     </row>
     <row r="310" spans="2:10" ht="15">
       <c r="B310" s="74" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="C310" s="71"/>
       <c r="D310" s="29"/>
@@ -35166,7 +35466,7 @@
     </row>
     <row r="311" spans="2:10" ht="15">
       <c r="B311" s="79" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C311" s="71"/>
       <c r="D311" s="29"/>
@@ -35179,7 +35479,7 @@
     </row>
     <row r="312" spans="2:10" ht="15">
       <c r="B312" s="79" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C312" s="71"/>
       <c r="D312" s="29"/>
@@ -35192,7 +35492,7 @@
     </row>
     <row r="313" spans="2:10" ht="15">
       <c r="B313" s="79" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C313" s="71"/>
       <c r="D313" s="29"/>
@@ -35205,7 +35505,7 @@
     </row>
     <row r="314" spans="2:10" ht="15">
       <c r="B314" s="74" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="C314" s="71"/>
       <c r="D314" s="29"/>
@@ -35218,7 +35518,7 @@
     </row>
     <row r="315" spans="2:10" ht="15">
       <c r="B315" s="79" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C315" s="71"/>
       <c r="D315" s="29"/>
@@ -35231,7 +35531,7 @@
     </row>
     <row r="316" spans="2:10" ht="15">
       <c r="B316" s="79" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C316" s="71"/>
       <c r="D316" s="29"/>
@@ -35244,7 +35544,7 @@
     </row>
     <row r="317" spans="2:10" ht="15">
       <c r="B317" s="74" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C317" s="71"/>
       <c r="D317" s="29"/>
@@ -35257,7 +35557,7 @@
     </row>
     <row r="318" spans="2:10" ht="15">
       <c r="B318" s="72" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="C318" s="68"/>
       <c r="D318" s="29"/>
@@ -35281,7 +35581,7 @@
     </row>
     <row r="320" spans="2:10" ht="15">
       <c r="B320" s="70" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C320" s="68"/>
       <c r="D320" s="29"/>
@@ -35294,7 +35594,7 @@
     </row>
     <row r="321" spans="2:10" ht="15">
       <c r="B321" s="70" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C321" s="68"/>
       <c r="D321" s="29"/>
@@ -35307,7 +35607,7 @@
     </row>
     <row r="322" spans="2:10" ht="15">
       <c r="B322" s="70" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C322" s="68"/>
       <c r="D322" s="29"/>
@@ -35320,7 +35620,7 @@
     </row>
     <row r="323" spans="2:10" ht="15">
       <c r="B323" s="72" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C323" s="68"/>
       <c r="D323" s="29"/>
@@ -35333,7 +35633,7 @@
     </row>
     <row r="324" spans="2:10" ht="15">
       <c r="B324" s="74" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="C324" s="68"/>
       <c r="D324" s="29"/>
@@ -35346,7 +35646,7 @@
     </row>
     <row r="325" spans="2:10" ht="15">
       <c r="B325" s="74" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="C325" s="68"/>
       <c r="D325" s="29"/>
@@ -35359,7 +35659,7 @@
     </row>
     <row r="326" spans="2:10" ht="15">
       <c r="B326" s="74" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C326" s="68"/>
       <c r="D326" s="29"/>
@@ -35372,7 +35672,7 @@
     </row>
     <row r="327" spans="2:10" ht="15">
       <c r="B327" s="72" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C327" s="68"/>
       <c r="D327" s="29"/>
@@ -35396,7 +35696,7 @@
     </row>
     <row r="329" spans="2:10" ht="15">
       <c r="B329" s="70" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C329" s="68"/>
       <c r="D329" s="29"/>
@@ -35409,7 +35709,7 @@
     </row>
     <row r="330" spans="2:10" ht="15">
       <c r="B330" s="72" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C330" s="68"/>
       <c r="D330" s="29"/>
@@ -35422,7 +35722,7 @@
     </row>
     <row r="331" spans="2:10" ht="15">
       <c r="B331" s="70" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C331" s="68"/>
       <c r="D331" s="29"/>
@@ -35435,7 +35735,7 @@
     </row>
     <row r="332" spans="2:10" ht="15">
       <c r="B332" s="72" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C332" s="68"/>
       <c r="D332" s="29"/>
@@ -35448,7 +35748,7 @@
     </row>
     <row r="333" spans="2:10" ht="15">
       <c r="B333" s="70" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C333" s="68"/>
       <c r="D333" s="29"/>
@@ -35461,7 +35761,7 @@
     </row>
     <row r="334" spans="2:10" ht="15">
       <c r="B334" s="72" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C334" s="68"/>
       <c r="D334" s="29"/>
@@ -35474,7 +35774,7 @@
     </row>
     <row r="335" spans="2:10" ht="15">
       <c r="B335" s="70" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="C335" s="68"/>
       <c r="D335" s="29"/>
@@ -35487,7 +35787,7 @@
     </row>
     <row r="336" spans="2:10" ht="15">
       <c r="B336" s="70" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="C336" s="68"/>
       <c r="D336" s="29"/>
@@ -35500,7 +35800,7 @@
     </row>
     <row r="337" spans="2:13" ht="15">
       <c r="B337" s="70" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="C337" s="68"/>
       <c r="D337" s="29"/>
@@ -35513,7 +35813,7 @@
     </row>
     <row r="338" spans="2:13" ht="15">
       <c r="B338" s="70" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C338" s="68"/>
       <c r="D338" s="29"/>
@@ -35526,7 +35826,7 @@
     </row>
     <row r="339" spans="2:13" ht="15">
       <c r="B339" s="72" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C339" s="68"/>
       <c r="D339" s="29"/>
@@ -35539,7 +35839,7 @@
     </row>
     <row r="340" spans="2:13" ht="15">
       <c r="B340" s="67" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C340" s="29"/>
       <c r="D340" s="29"/>
@@ -35552,7 +35852,7 @@
     </row>
     <row r="341" spans="2:13" ht="15">
       <c r="B341" s="28" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C341" s="29"/>
       <c r="D341" s="29"/>
@@ -35576,7 +35876,7 @@
     </row>
     <row r="343" spans="2:13" ht="15">
       <c r="B343" s="32" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C343" s="29"/>
       <c r="D343" s="29"/>
@@ -35589,7 +35889,7 @@
     </row>
     <row r="344" spans="2:13" ht="15">
       <c r="B344" s="28" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C344" s="29"/>
       <c r="D344" s="29"/>
@@ -35602,7 +35902,7 @@
     </row>
     <row r="345" spans="2:13" ht="15">
       <c r="B345" s="66" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="C345" s="29"/>
       <c r="D345" s="29"/>
@@ -35615,7 +35915,7 @@
     </row>
     <row r="346" spans="2:13" ht="15">
       <c r="B346" s="67" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C346" s="29"/>
       <c r="D346" s="29"/>
@@ -35628,7 +35928,7 @@
     </row>
     <row r="347" spans="2:13" ht="15">
       <c r="B347" s="28" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C347" s="29"/>
       <c r="D347" s="29"/>
@@ -35644,12 +35944,12 @@
     </row>
     <row r="349" spans="2:13" ht="17.25">
       <c r="B349" s="83" t="s">
-        <v>303</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="351" spans="2:13" ht="15">
       <c r="B351" s="32" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C351" s="29"/>
       <c r="D351" s="29"/>
@@ -35665,7 +35965,7 @@
     </row>
     <row r="352" spans="2:13" ht="15">
       <c r="B352" s="28" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="C352" s="29"/>
       <c r="D352" s="29"/>
@@ -35681,7 +35981,7 @@
     </row>
     <row r="353" spans="2:13" ht="15">
       <c r="B353" s="66" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="C353" s="29"/>
       <c r="D353" s="29"/>
@@ -35697,7 +35997,7 @@
     </row>
     <row r="354" spans="2:13" ht="15">
       <c r="B354" s="67" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C354" s="29"/>
       <c r="D354" s="29"/>
@@ -35713,7 +36013,7 @@
     </row>
     <row r="355" spans="2:13" ht="15">
       <c r="B355" s="70" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C355" s="29"/>
       <c r="D355" s="29"/>
@@ -35729,7 +36029,7 @@
     </row>
     <row r="356" spans="2:13" ht="15">
       <c r="B356" s="72" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="C356" s="29"/>
       <c r="D356" s="29"/>
@@ -35745,7 +36045,7 @@
     </row>
     <row r="357" spans="2:13" ht="15">
       <c r="B357" s="79" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="C357" s="68"/>
       <c r="D357" s="29"/>
@@ -35761,7 +36061,7 @@
     </row>
     <row r="358" spans="2:13" ht="15">
       <c r="B358" s="74" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="C358" s="68"/>
       <c r="D358" s="29"/>
@@ -35777,7 +36077,7 @@
     </row>
     <row r="359" spans="2:13" ht="15">
       <c r="B359" s="79" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="C359" s="68"/>
       <c r="D359" s="29"/>
@@ -35793,7 +36093,7 @@
     </row>
     <row r="360" spans="2:13" ht="15">
       <c r="B360" s="74" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C360" s="68"/>
       <c r="D360" s="29"/>
@@ -35823,7 +36123,7 @@
     </row>
     <row r="362" spans="2:13" ht="15">
       <c r="B362" s="79" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C362" s="68"/>
       <c r="D362" s="29"/>
@@ -35839,7 +36139,7 @@
     </row>
     <row r="363" spans="2:13" ht="15">
       <c r="B363" s="74" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="C363" s="68"/>
       <c r="D363" s="29"/>
@@ -35855,7 +36155,7 @@
     </row>
     <row r="364" spans="2:13" ht="15">
       <c r="B364" s="80" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C364" s="71"/>
       <c r="D364" s="29"/>
@@ -35871,7 +36171,7 @@
     </row>
     <row r="365" spans="2:13" ht="15">
       <c r="B365" s="76" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="C365" s="71"/>
       <c r="D365" s="29"/>
@@ -35887,7 +36187,7 @@
     </row>
     <row r="366" spans="2:13" ht="15">
       <c r="B366" s="80" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="C366" s="71"/>
       <c r="D366" s="29"/>
@@ -35903,7 +36203,7 @@
     </row>
     <row r="367" spans="2:13" ht="15">
       <c r="B367" s="76" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C367" s="71"/>
       <c r="D367" s="29"/>
@@ -35919,7 +36219,7 @@
     </row>
     <row r="368" spans="2:13" ht="15">
       <c r="B368" s="80" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="C368" s="71"/>
       <c r="D368" s="29"/>
@@ -35935,7 +36235,7 @@
     </row>
     <row r="369" spans="2:13" ht="15">
       <c r="B369" s="76" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="C369" s="71"/>
       <c r="D369" s="29"/>
@@ -35951,7 +36251,7 @@
     </row>
     <row r="370" spans="2:13" ht="15">
       <c r="B370" s="80" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="C370" s="71"/>
       <c r="D370" s="29"/>
@@ -35967,7 +36267,7 @@
     </row>
     <row r="371" spans="2:13" ht="15">
       <c r="B371" s="76" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="C371" s="71"/>
       <c r="D371" s="29"/>
@@ -35983,7 +36283,7 @@
     </row>
     <row r="372" spans="2:13" ht="15">
       <c r="B372" s="74" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="C372" s="68"/>
       <c r="D372" s="29"/>
@@ -36013,7 +36313,7 @@
     </row>
     <row r="374" spans="2:13" ht="15">
       <c r="B374" s="79" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="C374" s="68"/>
       <c r="D374" s="29"/>
@@ -36029,7 +36329,7 @@
     </row>
     <row r="375" spans="2:13" ht="15">
       <c r="B375" s="79" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C375" s="68"/>
       <c r="D375" s="29"/>
@@ -36045,7 +36345,7 @@
     </row>
     <row r="376" spans="2:13" ht="15">
       <c r="B376" s="74" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C376" s="68"/>
       <c r="D376" s="29"/>
@@ -36061,7 +36361,7 @@
     </row>
     <row r="377" spans="2:13" ht="15">
       <c r="B377" s="80" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="C377" s="68"/>
       <c r="D377" s="29"/>
@@ -36077,7 +36377,7 @@
     </row>
     <row r="378" spans="2:13" ht="15">
       <c r="B378" s="76" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C378" s="68"/>
       <c r="D378" s="29"/>
@@ -36093,7 +36393,7 @@
     </row>
     <row r="379" spans="2:13" ht="15">
       <c r="B379" s="80" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C379" s="68"/>
       <c r="D379" s="29"/>
@@ -36109,7 +36409,7 @@
     </row>
     <row r="380" spans="2:13" ht="15">
       <c r="B380" s="76" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C380" s="68"/>
       <c r="D380" s="29"/>
@@ -36125,7 +36425,7 @@
     </row>
     <row r="381" spans="2:13" ht="15">
       <c r="B381" s="74" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C381" s="68"/>
       <c r="D381" s="29"/>
@@ -36155,7 +36455,7 @@
     </row>
     <row r="383" spans="2:13" ht="15">
       <c r="B383" s="79" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C383" s="68"/>
       <c r="D383" s="29"/>
@@ -36171,7 +36471,7 @@
     </row>
     <row r="384" spans="2:13" ht="15">
       <c r="B384" s="79" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C384" s="68"/>
       <c r="D384" s="29"/>
@@ -36187,7 +36487,7 @@
     </row>
     <row r="385" spans="2:13" ht="15">
       <c r="B385" s="74" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C385" s="68"/>
       <c r="D385" s="29"/>
@@ -36203,7 +36503,7 @@
     </row>
     <row r="386" spans="2:13" ht="15">
       <c r="B386" s="80" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C386" s="68"/>
       <c r="D386" s="29"/>
@@ -36219,7 +36519,7 @@
     </row>
     <row r="387" spans="2:13" ht="15">
       <c r="B387" s="76" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="C387" s="68"/>
       <c r="D387" s="29"/>
@@ -36235,7 +36535,7 @@
     </row>
     <row r="388" spans="2:13" ht="15">
       <c r="B388" s="80" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C388" s="68"/>
       <c r="D388" s="29"/>
@@ -36251,7 +36551,7 @@
     </row>
     <row r="389" spans="2:13" ht="15">
       <c r="B389" s="76" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C389" s="68"/>
       <c r="D389" s="29"/>
@@ -36267,7 +36567,7 @@
     </row>
     <row r="390" spans="2:13" ht="15">
       <c r="B390" s="74" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C390" s="68"/>
       <c r="D390" s="29"/>
@@ -36283,7 +36583,7 @@
     </row>
     <row r="391" spans="2:13" ht="15">
       <c r="B391" s="72" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="C391" s="29"/>
       <c r="D391" s="29"/>
@@ -36313,7 +36613,7 @@
     </row>
     <row r="393" spans="2:13" ht="15">
       <c r="B393" s="72" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C393" s="29"/>
       <c r="D393" s="29"/>
@@ -36329,7 +36629,7 @@
     </row>
     <row r="394" spans="2:13" ht="15">
       <c r="B394" s="72" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C394" s="29"/>
       <c r="D394" s="29"/>
@@ -36345,7 +36645,7 @@
     </row>
     <row r="395" spans="2:13" ht="15">
       <c r="B395" s="72" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="C395" s="29"/>
       <c r="D395" s="29"/>
@@ -36361,7 +36661,7 @@
     </row>
     <row r="396" spans="2:13" ht="15">
       <c r="B396" s="72" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C396" s="29"/>
       <c r="D396" s="29"/>
@@ -36377,7 +36677,7 @@
     </row>
     <row r="397" spans="2:13" ht="15">
       <c r="B397" s="72" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="C397" s="29"/>
       <c r="D397" s="29"/>
@@ -36393,7 +36693,7 @@
     </row>
     <row r="398" spans="2:13" ht="15">
       <c r="B398" s="72" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C398" s="29"/>
       <c r="D398" s="29"/>
@@ -36409,7 +36709,7 @@
     </row>
     <row r="399" spans="2:13" ht="15">
       <c r="B399" s="72" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="C399" s="29"/>
       <c r="D399" s="29"/>
@@ -36425,7 +36725,7 @@
     </row>
     <row r="400" spans="2:13" ht="15">
       <c r="B400" s="72" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C400" s="29"/>
       <c r="D400" s="29"/>
@@ -36441,7 +36741,7 @@
     </row>
     <row r="401" spans="2:13" ht="15">
       <c r="B401" s="72" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="C401" s="29"/>
       <c r="D401" s="29"/>
@@ -36457,7 +36757,7 @@
     </row>
     <row r="402" spans="2:13" ht="15">
       <c r="B402" s="72" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C402" s="29"/>
       <c r="D402" s="29"/>
@@ -36473,7 +36773,7 @@
     </row>
     <row r="403" spans="2:13" ht="15">
       <c r="B403" s="67" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C403" s="29"/>
       <c r="D403" s="29"/>
@@ -36489,7 +36789,7 @@
     </row>
     <row r="404" spans="2:13" ht="15">
       <c r="B404" s="28" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="C404" s="29"/>
       <c r="D404" s="29"/>
@@ -36508,22 +36808,22 @@
     </row>
     <row r="406" spans="2:13">
       <c r="B406" s="33" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="407" spans="2:13">
       <c r="B407" s="33" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
     </row>
     <row r="408" spans="2:13">
       <c r="B408" s="26" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="409" spans="2:13">
       <c r="B409" s="33" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="410" spans="2:13">
@@ -36534,12 +36834,12 @@
     </row>
     <row r="412" spans="2:13" ht="17.25">
       <c r="B412" s="83" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="414" spans="2:13" ht="15">
       <c r="B414" s="32" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C414" s="29"/>
       <c r="D414" s="29"/>
@@ -36553,7 +36853,7 @@
     </row>
     <row r="415" spans="2:13" ht="15">
       <c r="B415" s="32" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C415" s="29"/>
       <c r="D415" s="29"/>
@@ -36567,7 +36867,7 @@
     </row>
     <row r="416" spans="2:13" ht="15">
       <c r="B416" s="28" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="C416" s="29"/>
       <c r="D416" s="29"/>
@@ -36581,7 +36881,7 @@
     </row>
     <row r="417" spans="2:11" ht="15">
       <c r="B417" s="66" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="C417" s="29"/>
       <c r="D417" s="29"/>
@@ -36595,7 +36895,7 @@
     </row>
     <row r="418" spans="2:11" ht="15">
       <c r="B418" s="67" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C418" s="29"/>
       <c r="D418" s="29"/>
@@ -36609,7 +36909,7 @@
     </row>
     <row r="419" spans="2:11" ht="15">
       <c r="B419" s="66" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="C419" s="29"/>
       <c r="D419" s="29"/>
@@ -36623,7 +36923,7 @@
     </row>
     <row r="420" spans="2:11" ht="15">
       <c r="B420" s="67" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="C420" s="29"/>
       <c r="D420" s="29"/>
@@ -36637,7 +36937,7 @@
     </row>
     <row r="421" spans="2:11" ht="15">
       <c r="B421" s="66" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C421" s="29"/>
       <c r="D421" s="29"/>
@@ -36651,7 +36951,7 @@
     </row>
     <row r="422" spans="2:11" ht="15">
       <c r="B422" s="67" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C422" s="29"/>
       <c r="D422" s="29"/>
@@ -36665,7 +36965,7 @@
     </row>
     <row r="423" spans="2:11" ht="15">
       <c r="B423" s="72" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C423" s="68"/>
       <c r="D423" s="29"/>
@@ -36679,7 +36979,7 @@
     </row>
     <row r="424" spans="2:11" ht="15">
       <c r="B424" s="74" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C424" s="68"/>
       <c r="D424" s="29"/>
@@ -36693,7 +36993,7 @@
     </row>
     <row r="425" spans="2:11" ht="15">
       <c r="B425" s="74" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C425" s="68"/>
       <c r="D425" s="29"/>
@@ -36707,7 +37007,7 @@
     </row>
     <row r="426" spans="2:11" ht="15">
       <c r="B426" s="74" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C426" s="68"/>
       <c r="D426" s="29"/>
@@ -36721,7 +37021,7 @@
     </row>
     <row r="427" spans="2:11" ht="15">
       <c r="B427" s="74" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C427" s="68"/>
       <c r="D427" s="29"/>
@@ -36747,7 +37047,7 @@
     </row>
     <row r="429" spans="2:11" ht="15">
       <c r="B429" s="74" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C429" s="68"/>
       <c r="D429" s="29"/>
@@ -36761,7 +37061,7 @@
     </row>
     <row r="430" spans="2:11" ht="15">
       <c r="B430" s="76" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C430" s="68"/>
       <c r="D430" s="29"/>
@@ -36775,7 +37075,7 @@
     </row>
     <row r="431" spans="2:11" ht="15">
       <c r="B431" s="81" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C431" s="68"/>
       <c r="D431" s="29"/>
@@ -36789,7 +37089,7 @@
     </row>
     <row r="432" spans="2:11" ht="15">
       <c r="B432" s="76" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C432" s="68"/>
       <c r="D432" s="29"/>
@@ -36803,7 +37103,7 @@
     </row>
     <row r="433" spans="2:11" ht="15">
       <c r="B433" s="74" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C433" s="68"/>
       <c r="D433" s="29"/>
@@ -36829,7 +37129,7 @@
     </row>
     <row r="435" spans="2:11" ht="15">
       <c r="B435" s="79" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="C435" s="68"/>
       <c r="D435" s="29"/>
@@ -36843,7 +37143,7 @@
     </row>
     <row r="436" spans="2:11" ht="15">
       <c r="B436" s="79" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C436" s="68"/>
       <c r="D436" s="29"/>
@@ -36857,7 +37157,7 @@
     </row>
     <row r="437" spans="2:11" ht="15">
       <c r="B437" s="79" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C437" s="68"/>
       <c r="D437" s="29"/>
@@ -36871,7 +37171,7 @@
     </row>
     <row r="438" spans="2:11" ht="15">
       <c r="B438" s="74" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C438" s="68"/>
       <c r="D438" s="29"/>
@@ -36885,7 +37185,7 @@
     </row>
     <row r="439" spans="2:11" ht="15">
       <c r="B439" s="80" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="C439" s="68"/>
       <c r="D439" s="29"/>
@@ -36899,7 +37199,7 @@
     </row>
     <row r="440" spans="2:11" ht="15">
       <c r="B440" s="76" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C440" s="68"/>
       <c r="D440" s="29"/>
@@ -36913,7 +37213,7 @@
     </row>
     <row r="441" spans="2:11" ht="15">
       <c r="B441" s="84" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="C441" s="71"/>
       <c r="D441" s="29"/>
@@ -36927,7 +37227,7 @@
     </row>
     <row r="442" spans="2:11" ht="15">
       <c r="B442" s="81" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C442" s="71"/>
       <c r="D442" s="29"/>
@@ -36941,7 +37241,7 @@
     </row>
     <row r="443" spans="2:11" ht="15">
       <c r="B443" s="84" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="C443" s="71"/>
       <c r="D443" s="29"/>
@@ -36955,7 +37255,7 @@
     </row>
     <row r="444" spans="2:11" ht="15">
       <c r="B444" s="81" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C444" s="71"/>
       <c r="D444" s="29"/>
@@ -36969,7 +37269,7 @@
     </row>
     <row r="445" spans="2:11" ht="15">
       <c r="B445" s="84" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="C445" s="71"/>
       <c r="D445" s="29"/>
@@ -36983,7 +37283,7 @@
     </row>
     <row r="446" spans="2:11" ht="15">
       <c r="B446" s="81" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C446" s="71"/>
       <c r="D446" s="29"/>
@@ -37009,7 +37309,7 @@
     </row>
     <row r="448" spans="2:11" ht="15">
       <c r="B448" s="84" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C448" s="71"/>
       <c r="D448" s="29"/>
@@ -37023,7 +37323,7 @@
     </row>
     <row r="449" spans="2:12" ht="15">
       <c r="B449" s="81" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="C449" s="71"/>
       <c r="D449" s="29"/>
@@ -37037,7 +37337,7 @@
     </row>
     <row r="450" spans="2:12" ht="15">
       <c r="B450" s="85" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C450" s="71"/>
       <c r="D450" s="29"/>
@@ -37051,7 +37351,7 @@
     </row>
     <row r="451" spans="2:12" ht="15">
       <c r="B451" s="81" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C451" s="71"/>
       <c r="D451" s="29"/>
@@ -37065,7 +37365,7 @@
     </row>
     <row r="452" spans="2:12" ht="15">
       <c r="B452" s="76" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C452" s="68"/>
       <c r="D452" s="29"/>
@@ -37079,7 +37379,7 @@
     </row>
     <row r="453" spans="2:12" ht="15">
       <c r="B453" s="74" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C453" s="68"/>
       <c r="D453" s="29"/>
@@ -37093,7 +37393,7 @@
     </row>
     <row r="454" spans="2:12" ht="15">
       <c r="B454" s="72" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C454" s="68"/>
       <c r="D454" s="29"/>
@@ -37107,7 +37407,7 @@
     </row>
     <row r="455" spans="2:12" ht="15">
       <c r="B455" s="67" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C455" s="29"/>
       <c r="D455" s="29"/>
@@ -37121,7 +37421,7 @@
     </row>
     <row r="456" spans="2:12" ht="15">
       <c r="B456" s="28" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C456" s="29"/>
       <c r="D456" s="29"/>
@@ -37138,12 +37438,12 @@
     </row>
     <row r="458" spans="2:12" ht="17.25">
       <c r="B458" s="83" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="460" spans="2:12" ht="15">
       <c r="B460" s="32" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C460" s="29"/>
       <c r="D460" s="29"/>
@@ -37158,7 +37458,7 @@
     </row>
     <row r="461" spans="2:12" ht="15">
       <c r="B461" s="28" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C461" s="29"/>
       <c r="D461" s="29"/>
@@ -37173,7 +37473,7 @@
     </row>
     <row r="462" spans="2:12" ht="15">
       <c r="B462" s="66" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C462" s="29"/>
       <c r="D462" s="29"/>
@@ -37188,7 +37488,7 @@
     </row>
     <row r="463" spans="2:12" ht="15">
       <c r="B463" s="67" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C463" s="29"/>
       <c r="D463" s="29"/>
@@ -37203,7 +37503,7 @@
     </row>
     <row r="464" spans="2:12" ht="15">
       <c r="B464" s="66" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C464" s="29"/>
       <c r="D464" s="29"/>
@@ -37218,7 +37518,7 @@
     </row>
     <row r="465" spans="2:12" ht="15">
       <c r="B465" s="67" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="C465" s="29"/>
       <c r="D465" s="29"/>
@@ -37233,7 +37533,7 @@
     </row>
     <row r="466" spans="2:12" ht="15">
       <c r="B466" s="28" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C466" s="29"/>
       <c r="D466" s="29"/>
@@ -37261,7 +37561,7 @@
     </row>
     <row r="468" spans="2:12" ht="15">
       <c r="B468" s="32" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C468" s="29"/>
       <c r="D468" s="29"/>
@@ -37276,7 +37576,7 @@
     </row>
     <row r="469" spans="2:12" ht="15">
       <c r="B469" s="28" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="C469" s="29"/>
       <c r="D469" s="29"/>
@@ -37291,7 +37591,7 @@
     </row>
     <row r="470" spans="2:12" ht="15">
       <c r="B470" s="66" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C470" s="29"/>
       <c r="D470" s="29"/>
@@ -37306,7 +37606,7 @@
     </row>
     <row r="471" spans="2:12" ht="15">
       <c r="B471" s="67" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C471" s="29"/>
       <c r="D471" s="29"/>
@@ -37321,7 +37621,7 @@
     </row>
     <row r="472" spans="2:12" ht="15">
       <c r="B472" s="66" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C472" s="29"/>
       <c r="D472" s="29"/>
@@ -37336,7 +37636,7 @@
     </row>
     <row r="473" spans="2:12" ht="15">
       <c r="B473" s="67" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C473" s="29"/>
       <c r="D473" s="29"/>
@@ -37364,7 +37664,7 @@
     </row>
     <row r="475" spans="2:12" ht="15">
       <c r="B475" s="66" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C475" s="29"/>
       <c r="D475" s="29"/>
@@ -37379,7 +37679,7 @@
     </row>
     <row r="476" spans="2:12" ht="15">
       <c r="B476" s="67" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C476" s="29"/>
       <c r="D476" s="29"/>
@@ -37394,7 +37694,7 @@
     </row>
     <row r="477" spans="2:12" ht="15">
       <c r="B477" s="70" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C477" s="29"/>
       <c r="D477" s="29"/>
@@ -37409,7 +37709,7 @@
     </row>
     <row r="478" spans="2:12" ht="15">
       <c r="B478" s="72" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C478" s="29"/>
       <c r="D478" s="29"/>
@@ -37424,7 +37724,7 @@
     </row>
     <row r="479" spans="2:12" ht="15">
       <c r="B479" s="79" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C479" s="29"/>
       <c r="D479" s="29"/>
@@ -37439,7 +37739,7 @@
     </row>
     <row r="480" spans="2:12" ht="15">
       <c r="B480" s="74" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C480" s="29"/>
       <c r="D480" s="29"/>
@@ -37454,7 +37754,7 @@
     </row>
     <row r="481" spans="2:12" ht="15">
       <c r="B481" s="79" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C481" s="29"/>
       <c r="D481" s="29"/>
@@ -37469,7 +37769,7 @@
     </row>
     <row r="482" spans="2:12" ht="15">
       <c r="B482" s="74" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="C482" s="29"/>
       <c r="D482" s="29"/>
@@ -37484,7 +37784,7 @@
     </row>
     <row r="483" spans="2:12" ht="15">
       <c r="B483" s="79" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="C483" s="29"/>
       <c r="D483" s="29"/>
@@ -37499,7 +37799,7 @@
     </row>
     <row r="484" spans="2:12" ht="15">
       <c r="B484" s="74" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C484" s="29"/>
       <c r="D484" s="29"/>
@@ -37514,7 +37814,7 @@
     </row>
     <row r="485" spans="2:12" ht="15">
       <c r="B485" s="79" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C485" s="29"/>
       <c r="D485" s="29"/>
@@ -37529,7 +37829,7 @@
     </row>
     <row r="486" spans="2:12" ht="15">
       <c r="B486" s="74" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C486" s="29"/>
       <c r="D486" s="29"/>
@@ -37544,7 +37844,7 @@
     </row>
     <row r="487" spans="2:12" ht="15">
       <c r="B487" s="79" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="C487" s="29"/>
       <c r="D487" s="29"/>
@@ -37559,7 +37859,7 @@
     </row>
     <row r="488" spans="2:12" ht="15">
       <c r="B488" s="74" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C488" s="29"/>
       <c r="D488" s="29"/>
@@ -37574,7 +37874,7 @@
     </row>
     <row r="489" spans="2:12" ht="15">
       <c r="B489" s="79" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C489" s="29"/>
       <c r="D489" s="29"/>
@@ -37589,7 +37889,7 @@
     </row>
     <row r="490" spans="2:12" ht="15">
       <c r="B490" s="74" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C490" s="29"/>
       <c r="D490" s="29"/>
@@ -37604,7 +37904,7 @@
     </row>
     <row r="491" spans="2:12" ht="15">
       <c r="B491" s="79" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="C491" s="29"/>
       <c r="D491" s="29"/>
@@ -37619,7 +37919,7 @@
     </row>
     <row r="492" spans="2:12" ht="15">
       <c r="B492" s="74" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C492" s="29"/>
       <c r="D492" s="29"/>
@@ -37634,7 +37934,7 @@
     </row>
     <row r="493" spans="2:12" ht="15">
       <c r="B493" s="72" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C493" s="29"/>
       <c r="D493" s="29"/>
@@ -37649,7 +37949,7 @@
     </row>
     <row r="494" spans="2:12" ht="15">
       <c r="B494" s="67" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="C494" s="29"/>
       <c r="D494" s="29"/>
@@ -37664,7 +37964,7 @@
     </row>
     <row r="495" spans="2:12" ht="15">
       <c r="B495" s="28" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C495" s="29"/>
       <c r="D495" s="29"/>
@@ -37682,12 +37982,12 @@
     </row>
     <row r="497" spans="2:13" ht="17.25">
       <c r="B497" s="35" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="499" spans="2:13" ht="15">
       <c r="B499" s="32" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C499" s="29"/>
       <c r="D499" s="29"/>
@@ -37703,7 +38003,7 @@
     </row>
     <row r="500" spans="2:13" ht="15">
       <c r="B500" s="28" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C500" s="29"/>
       <c r="D500" s="29"/>
@@ -37719,7 +38019,7 @@
     </row>
     <row r="501" spans="2:13" ht="15">
       <c r="B501" s="32" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="C501" s="29"/>
       <c r="D501" s="29"/>
@@ -37735,7 +38035,7 @@
     </row>
     <row r="502" spans="2:13" ht="15">
       <c r="B502" s="28" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C502" s="29"/>
       <c r="D502" s="29"/>
@@ -37751,7 +38051,7 @@
     </row>
     <row r="503" spans="2:13" ht="15">
       <c r="B503" s="32" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="C503" s="29"/>
       <c r="D503" s="29"/>
@@ -37767,7 +38067,7 @@
     </row>
     <row r="504" spans="2:13" ht="15">
       <c r="B504" s="32" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="C504" s="29"/>
       <c r="D504" s="29"/>
@@ -37783,7 +38083,7 @@
     </row>
     <row r="505" spans="2:13" ht="15">
       <c r="B505" s="32" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C505" s="29"/>
       <c r="D505" s="29"/>
@@ -37799,7 +38099,7 @@
     </row>
     <row r="506" spans="2:13" ht="15">
       <c r="B506" s="28" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C506" s="29"/>
       <c r="D506" s="29"/>
@@ -37815,7 +38115,7 @@
     </row>
     <row r="507" spans="2:13" ht="15">
       <c r="B507" s="32" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="C507" s="29"/>
       <c r="D507" s="29"/>
@@ -37831,7 +38131,7 @@
     </row>
     <row r="508" spans="2:13" ht="15">
       <c r="B508" s="28" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C508" s="29"/>
       <c r="D508" s="29"/>
@@ -37847,7 +38147,7 @@
     </row>
     <row r="509" spans="2:13" ht="15">
       <c r="B509" s="66" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C509" s="68"/>
       <c r="D509" s="29"/>
@@ -37863,7 +38163,7 @@
     </row>
     <row r="510" spans="2:13" ht="15">
       <c r="B510" s="67" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="C510" s="68"/>
       <c r="D510" s="29"/>
@@ -37879,7 +38179,7 @@
     </row>
     <row r="511" spans="2:13" ht="15">
       <c r="B511" s="28" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C511" s="29"/>
       <c r="D511" s="29"/>
@@ -37895,7 +38195,7 @@
     </row>
     <row r="512" spans="2:13" ht="15">
       <c r="B512" s="32" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="C512" s="29"/>
       <c r="D512" s="29"/>
@@ -37911,7 +38211,7 @@
     </row>
     <row r="513" spans="2:13" ht="15">
       <c r="B513" s="28" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C513" s="29"/>
       <c r="D513" s="29"/>
@@ -37941,7 +38241,7 @@
     </row>
     <row r="515" spans="2:13" ht="15">
       <c r="B515" s="32" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C515" s="29"/>
       <c r="D515" s="29"/>
@@ -37957,7 +38257,7 @@
     </row>
     <row r="516" spans="2:13" ht="15">
       <c r="B516" s="28" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="C516" s="29"/>
       <c r="D516" s="29"/>
@@ -37973,7 +38273,7 @@
     </row>
     <row r="517" spans="2:13" ht="15">
       <c r="B517" s="66" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C517" s="29"/>
       <c r="D517" s="29"/>
@@ -37989,7 +38289,7 @@
     </row>
     <row r="518" spans="2:13" ht="15">
       <c r="B518" s="67" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C518" s="29"/>
       <c r="D518" s="29"/>
@@ -38005,7 +38305,7 @@
     </row>
     <row r="519" spans="2:13" ht="15">
       <c r="B519" s="70" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="C519" s="68"/>
       <c r="D519" s="29"/>
@@ -38021,7 +38321,7 @@
     </row>
     <row r="520" spans="2:13" ht="15">
       <c r="B520" s="72" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C520" s="68"/>
       <c r="D520" s="29"/>
@@ -38037,7 +38337,7 @@
     </row>
     <row r="521" spans="2:13" ht="15">
       <c r="B521" s="70" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C521" s="68"/>
       <c r="D521" s="29"/>
@@ -38053,7 +38353,7 @@
     </row>
     <row r="522" spans="2:13" ht="15">
       <c r="B522" s="72" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C522" s="68"/>
       <c r="D522" s="29"/>
@@ -38069,7 +38369,7 @@
     </row>
     <row r="523" spans="2:13" ht="15">
       <c r="B523" s="70" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="C523" s="68"/>
       <c r="D523" s="29"/>
@@ -38085,7 +38385,7 @@
     </row>
     <row r="524" spans="2:13" ht="15">
       <c r="B524" s="72" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C524" s="68"/>
       <c r="D524" s="29"/>
@@ -38101,7 +38401,7 @@
     </row>
     <row r="525" spans="2:13" ht="15">
       <c r="B525" s="70" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="C525" s="68"/>
       <c r="D525" s="29"/>
@@ -38117,7 +38417,7 @@
     </row>
     <row r="526" spans="2:13" ht="15">
       <c r="B526" s="72" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="C526" s="68"/>
       <c r="D526" s="29"/>
@@ -38133,7 +38433,7 @@
     </row>
     <row r="527" spans="2:13" ht="15">
       <c r="B527" s="70" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C527" s="68"/>
       <c r="D527" s="29"/>
@@ -38149,7 +38449,7 @@
     </row>
     <row r="528" spans="2:13" ht="15">
       <c r="B528" s="72" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="C528" s="68"/>
       <c r="D528" s="29"/>
@@ -38165,7 +38465,7 @@
     </row>
     <row r="529" spans="2:13" ht="15">
       <c r="B529" s="67" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C529" s="29"/>
       <c r="D529" s="29"/>
@@ -38181,7 +38481,7 @@
     </row>
     <row r="530" spans="2:13" ht="15">
       <c r="B530" s="28" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C530" s="29"/>
       <c r="D530" s="29"/>
@@ -38211,7 +38511,7 @@
     </row>
     <row r="532" spans="2:13" ht="15">
       <c r="B532" s="32" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C532" s="29"/>
       <c r="D532" s="29"/>
@@ -38227,7 +38527,7 @@
     </row>
     <row r="533" spans="2:13" ht="15">
       <c r="B533" s="28" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C533" s="29"/>
       <c r="D533" s="29"/>
@@ -38243,7 +38543,7 @@
     </row>
     <row r="534" spans="2:13" ht="15">
       <c r="B534" s="66" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C534" s="29"/>
       <c r="D534" s="29"/>
@@ -38259,7 +38559,7 @@
     </row>
     <row r="535" spans="2:13" ht="15">
       <c r="B535" s="67" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C535" s="29"/>
       <c r="D535" s="29"/>
@@ -38275,7 +38575,7 @@
     </row>
     <row r="536" spans="2:13" ht="15">
       <c r="B536" s="70" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C536" s="68"/>
       <c r="D536" s="29"/>
@@ -38291,7 +38591,7 @@
     </row>
     <row r="537" spans="2:13" ht="15">
       <c r="B537" s="72" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C537" s="68"/>
       <c r="D537" s="29"/>
@@ -38307,7 +38607,7 @@
     </row>
     <row r="538" spans="2:13" ht="15">
       <c r="B538" s="70" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C538" s="68"/>
       <c r="D538" s="29"/>
@@ -38323,7 +38623,7 @@
     </row>
     <row r="539" spans="2:13" ht="15">
       <c r="B539" s="72" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C539" s="68"/>
       <c r="D539" s="29"/>
@@ -38339,7 +38639,7 @@
     </row>
     <row r="540" spans="2:13" ht="15">
       <c r="B540" s="70" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C540" s="68"/>
       <c r="D540" s="29"/>
@@ -38355,7 +38655,7 @@
     </row>
     <row r="541" spans="2:13" ht="15">
       <c r="B541" s="72" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="C541" s="68"/>
       <c r="D541" s="29"/>
@@ -38371,7 +38671,7 @@
     </row>
     <row r="542" spans="2:13" ht="15">
       <c r="B542" s="70" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="C542" s="68"/>
       <c r="D542" s="29"/>
@@ -38387,7 +38687,7 @@
     </row>
     <row r="543" spans="2:13" ht="15">
       <c r="B543" s="72" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C543" s="68"/>
       <c r="D543" s="29"/>
@@ -38417,7 +38717,7 @@
     </row>
     <row r="545" spans="2:13" ht="15">
       <c r="B545" s="70" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C545" s="68"/>
       <c r="D545" s="29"/>
@@ -38433,7 +38733,7 @@
     </row>
     <row r="546" spans="2:13" ht="15">
       <c r="B546" s="72" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C546" s="68"/>
       <c r="D546" s="29"/>
@@ -38449,7 +38749,7 @@
     </row>
     <row r="547" spans="2:13" ht="15">
       <c r="B547" s="74" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C547" s="68"/>
       <c r="D547" s="29"/>
@@ -38465,7 +38765,7 @@
     </row>
     <row r="548" spans="2:13" ht="15">
       <c r="B548" s="74" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C548" s="68"/>
       <c r="D548" s="29"/>
@@ -38481,7 +38781,7 @@
     </row>
     <row r="549" spans="2:13" ht="15">
       <c r="B549" s="72" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="C549" s="68"/>
       <c r="D549" s="29"/>
@@ -38511,7 +38811,7 @@
     </row>
     <row r="551" spans="2:13" ht="15">
       <c r="B551" s="70" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="C551" s="68"/>
       <c r="D551" s="29"/>
@@ -38527,7 +38827,7 @@
     </row>
     <row r="552" spans="2:13" ht="15">
       <c r="B552" s="72" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="C552" s="68"/>
       <c r="D552" s="29"/>
@@ -38543,7 +38843,7 @@
     </row>
     <row r="553" spans="2:13" ht="15">
       <c r="B553" s="70" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="C553" s="68"/>
       <c r="D553" s="29"/>
@@ -38559,7 +38859,7 @@
     </row>
     <row r="554" spans="2:13" ht="15">
       <c r="B554" s="72" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="C554" s="68"/>
       <c r="D554" s="29"/>
@@ -38575,7 +38875,7 @@
     </row>
     <row r="555" spans="2:13" ht="15">
       <c r="B555" s="70" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C555" s="68"/>
       <c r="D555" s="29"/>
@@ -38591,7 +38891,7 @@
     </row>
     <row r="556" spans="2:13" ht="15">
       <c r="B556" s="72" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C556" s="68"/>
       <c r="D556" s="29"/>
@@ -38607,7 +38907,7 @@
     </row>
     <row r="557" spans="2:13" ht="15">
       <c r="B557" s="74" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="C557" s="68"/>
       <c r="D557" s="29"/>
@@ -38623,7 +38923,7 @@
     </row>
     <row r="558" spans="2:13" ht="15">
       <c r="B558" s="72" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C558" s="68"/>
       <c r="D558" s="29"/>
@@ -38639,7 +38939,7 @@
     </row>
     <row r="559" spans="2:13" ht="15">
       <c r="B559" s="70" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C559" s="68"/>
       <c r="D559" s="29"/>
@@ -38655,7 +38955,7 @@
     </row>
     <row r="560" spans="2:13" ht="15">
       <c r="B560" s="72" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C560" s="68"/>
       <c r="D560" s="29"/>
@@ -38671,7 +38971,7 @@
     </row>
     <row r="561" spans="2:13" ht="15">
       <c r="B561" s="67" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="C561" s="29"/>
       <c r="D561" s="29"/>
@@ -38687,7 +38987,7 @@
     </row>
     <row r="562" spans="2:13" ht="15">
       <c r="B562" s="28" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C562" s="29"/>
       <c r="D562" s="29"/>
@@ -38717,7 +39017,7 @@
     </row>
     <row r="564" spans="2:13" ht="15">
       <c r="B564" s="32" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="C564" s="29"/>
       <c r="D564" s="29"/>
@@ -38733,7 +39033,7 @@
     </row>
     <row r="565" spans="2:13" ht="15">
       <c r="B565" s="28" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C565" s="29"/>
       <c r="D565" s="29"/>
@@ -38749,7 +39049,7 @@
     </row>
     <row r="566" spans="2:13" ht="15">
       <c r="B566" s="66" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C566" s="29"/>
       <c r="D566" s="29"/>
@@ -38765,7 +39065,7 @@
     </row>
     <row r="567" spans="2:13" ht="15">
       <c r="B567" s="67" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="C567" s="29"/>
       <c r="D567" s="29"/>
@@ -38781,7 +39081,7 @@
     </row>
     <row r="568" spans="2:13" ht="15">
       <c r="B568" s="72" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C568" s="29"/>
       <c r="D568" s="29"/>
@@ -38797,7 +39097,7 @@
     </row>
     <row r="569" spans="2:13" ht="15">
       <c r="B569" s="72" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C569" s="29"/>
       <c r="D569" s="29"/>
@@ -38813,7 +39113,7 @@
     </row>
     <row r="570" spans="2:13" ht="15">
       <c r="B570" s="72" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C570" s="29"/>
       <c r="D570" s="29"/>
@@ -38829,7 +39129,7 @@
     </row>
     <row r="571" spans="2:13" ht="15">
       <c r="B571" s="72" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C571" s="29"/>
       <c r="D571" s="29"/>
@@ -38845,7 +39145,7 @@
     </row>
     <row r="572" spans="2:13" ht="15">
       <c r="B572" s="72" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C572" s="29"/>
       <c r="D572" s="29"/>
@@ -38861,7 +39161,7 @@
     </row>
     <row r="573" spans="2:13" ht="15">
       <c r="B573" s="72" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="C573" s="29"/>
       <c r="D573" s="29"/>
@@ -38877,7 +39177,7 @@
     </row>
     <row r="574" spans="2:13" ht="15">
       <c r="B574" s="72" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C574" s="29"/>
       <c r="D574" s="29"/>
@@ -38893,7 +39193,7 @@
     </row>
     <row r="575" spans="2:13" ht="15">
       <c r="B575" s="72" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C575" s="29"/>
       <c r="D575" s="29"/>
@@ -38909,7 +39209,7 @@
     </row>
     <row r="576" spans="2:13" ht="15">
       <c r="B576" s="67" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C576" s="29"/>
       <c r="D576" s="29"/>
@@ -38925,7 +39225,7 @@
     </row>
     <row r="577" spans="2:13" ht="15">
       <c r="B577" s="28" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="C577" s="29"/>
       <c r="D577" s="29"/>
@@ -38955,7 +39255,7 @@
     </row>
     <row r="579" spans="2:13" ht="15">
       <c r="B579" s="32" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="C579" s="29"/>
       <c r="D579" s="29"/>
@@ -38971,7 +39271,7 @@
     </row>
     <row r="580" spans="2:13" ht="15">
       <c r="B580" s="32" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="C580" s="29"/>
       <c r="D580" s="29"/>
@@ -38987,7 +39287,7 @@
     </row>
     <row r="581" spans="2:13" ht="15">
       <c r="B581" s="28" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="C581" s="29"/>
       <c r="D581" s="29"/>
@@ -39003,7 +39303,7 @@
     </row>
     <row r="582" spans="2:13" ht="15">
       <c r="B582" s="66" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="C582" s="29"/>
       <c r="D582" s="29"/>
@@ -39019,7 +39319,7 @@
     </row>
     <row r="583" spans="2:13" ht="15">
       <c r="B583" s="67" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="C583" s="29"/>
       <c r="D583" s="29"/>
@@ -39035,7 +39335,7 @@
     </row>
     <row r="584" spans="2:13" ht="15">
       <c r="B584" s="70" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="C584" s="29"/>
       <c r="D584" s="29"/>
@@ -39051,7 +39351,7 @@
     </row>
     <row r="585" spans="2:13" ht="15">
       <c r="B585" s="72" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C585" s="29"/>
       <c r="D585" s="29"/>
@@ -39067,7 +39367,7 @@
     </row>
     <row r="586" spans="2:13" ht="15">
       <c r="B586" s="70" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="C586" s="29"/>
       <c r="D586" s="29"/>
@@ -39083,7 +39383,7 @@
     </row>
     <row r="587" spans="2:13" ht="15">
       <c r="B587" s="72" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C587" s="29"/>
       <c r="D587" s="29"/>
@@ -39099,7 +39399,7 @@
     </row>
     <row r="588" spans="2:13" ht="15">
       <c r="B588" s="70" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="C588" s="29"/>
       <c r="D588" s="29"/>
@@ -39115,7 +39415,7 @@
     </row>
     <row r="589" spans="2:13" ht="15">
       <c r="B589" s="72" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="C589" s="29"/>
       <c r="D589" s="29"/>
@@ -39131,7 +39431,7 @@
     </row>
     <row r="590" spans="2:13" ht="15">
       <c r="B590" s="70" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="C590" s="29"/>
       <c r="D590" s="29"/>
@@ -39147,7 +39447,7 @@
     </row>
     <row r="591" spans="2:13" ht="15">
       <c r="B591" s="72" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="C591" s="29"/>
       <c r="D591" s="29"/>
@@ -39163,7 +39463,7 @@
     </row>
     <row r="592" spans="2:13" ht="15">
       <c r="B592" s="67" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="C592" s="29"/>
       <c r="D592" s="29"/>
@@ -39179,7 +39479,7 @@
     </row>
     <row r="593" spans="2:13" ht="15">
       <c r="B593" s="28" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="C593" s="29"/>
       <c r="D593" s="29"/>
@@ -39209,7 +39509,7 @@
     </row>
     <row r="595" spans="2:13" ht="15">
       <c r="B595" s="32" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="C595" s="29"/>
       <c r="D595" s="29"/>
@@ -39225,7 +39525,7 @@
     </row>
     <row r="596" spans="2:13" ht="15">
       <c r="B596" s="28" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="C596" s="29"/>
       <c r="D596" s="29"/>
@@ -39241,7 +39541,7 @@
     </row>
     <row r="597" spans="2:13" ht="15">
       <c r="B597" s="66" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="C597" s="29"/>
       <c r="D597" s="29"/>
@@ -39257,7 +39557,7 @@
     </row>
     <row r="598" spans="2:13" ht="15">
       <c r="B598" s="67" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="C598" s="29"/>
       <c r="D598" s="29"/>
@@ -39273,7 +39573,7 @@
     </row>
     <row r="599" spans="2:13" ht="15">
       <c r="B599" s="66" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="C599" s="29"/>
       <c r="D599" s="29"/>
@@ -39289,7 +39589,7 @@
     </row>
     <row r="600" spans="2:13" ht="15">
       <c r="B600" s="67" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="C600" s="29"/>
       <c r="D600" s="29"/>
@@ -39305,7 +39605,7 @@
     </row>
     <row r="601" spans="2:13" ht="15">
       <c r="B601" s="67" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="C601" s="29"/>
       <c r="D601" s="29"/>
@@ -39321,7 +39621,7 @@
     </row>
     <row r="602" spans="2:13" ht="15">
       <c r="B602" s="66" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="C602" s="29"/>
       <c r="D602" s="29"/>
@@ -39337,7 +39637,7 @@
     </row>
     <row r="603" spans="2:13" ht="15">
       <c r="B603" s="67" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="C603" s="29"/>
       <c r="D603" s="29"/>
@@ -39353,7 +39653,7 @@
     </row>
     <row r="604" spans="2:13" ht="15">
       <c r="B604" s="66" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C604" s="29"/>
       <c r="D604" s="29"/>
@@ -39369,7 +39669,7 @@
     </row>
     <row r="605" spans="2:13" ht="15">
       <c r="B605" s="67" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="C605" s="29"/>
       <c r="D605" s="29"/>
@@ -39385,7 +39685,7 @@
     </row>
     <row r="606" spans="2:13" ht="15">
       <c r="B606" s="28" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="C606" s="29"/>
       <c r="D606" s="29"/>
@@ -39415,7 +39715,7 @@
     </row>
     <row r="608" spans="2:13" ht="15">
       <c r="B608" s="32" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C608" s="29"/>
       <c r="D608" s="29"/>
@@ -39431,7 +39731,7 @@
     </row>
     <row r="609" spans="1:22" ht="15">
       <c r="B609" s="28" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="C609" s="29"/>
       <c r="D609" s="29"/>
@@ -39447,7 +39747,7 @@
     </row>
     <row r="610" spans="1:22" ht="15">
       <c r="B610" s="66" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C610" s="29"/>
       <c r="D610" s="29"/>
@@ -39463,7 +39763,7 @@
     </row>
     <row r="611" spans="1:22" ht="15">
       <c r="B611" s="67" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="C611" s="29"/>
       <c r="D611" s="29"/>
@@ -39479,7 +39779,7 @@
     </row>
     <row r="612" spans="1:22" ht="15">
       <c r="B612" s="66" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="C612" s="29"/>
       <c r="D612" s="29"/>
@@ -39495,7 +39795,7 @@
     </row>
     <row r="613" spans="1:22" ht="15">
       <c r="B613" s="67" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="C613" s="29"/>
       <c r="D613" s="29"/>
@@ -39511,7 +39811,7 @@
     </row>
     <row r="614" spans="1:22" ht="15">
       <c r="B614" s="28" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="C614" s="29"/>
       <c r="D614" s="29"/>
@@ -39527,12 +39827,12 @@
     </row>
     <row r="618" spans="1:22" ht="23.25">
       <c r="A618" s="50" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="619" spans="1:22">
       <c r="B619" s="51" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="C619" s="51"/>
       <c r="D619" s="51"/>
@@ -39557,7 +39857,7 @@
     </row>
     <row r="620" spans="1:22">
       <c r="B620" s="51" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="C620" s="51"/>
       <c r="D620" s="51"/>
@@ -39582,7 +39882,7 @@
     </row>
     <row r="621" spans="1:22">
       <c r="B621" s="51" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="C621" s="51"/>
       <c r="D621" s="51"/>
@@ -39607,7 +39907,7 @@
     </row>
     <row r="622" spans="1:22">
       <c r="B622" s="51" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C622" s="51"/>
       <c r="D622" s="51"/>
@@ -39632,7 +39932,7 @@
     </row>
     <row r="623" spans="1:22">
       <c r="B623" s="51" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="C623" s="51"/>
       <c r="D623" s="51"/>
@@ -39657,7 +39957,7 @@
     </row>
     <row r="624" spans="1:22">
       <c r="B624" s="51" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="C624" s="51"/>
       <c r="D624" s="51"/>
@@ -39682,7 +39982,7 @@
     </row>
     <row r="625" spans="2:22">
       <c r="B625" s="51" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="C625" s="51"/>
       <c r="D625" s="51"/>
@@ -39707,7 +40007,7 @@
     </row>
     <row r="626" spans="2:22">
       <c r="B626" s="51" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="C626" s="51"/>
       <c r="D626" s="51"/>
@@ -39732,7 +40032,7 @@
     </row>
     <row r="627" spans="2:22">
       <c r="B627" s="51" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="C627" s="51"/>
       <c r="D627" s="51"/>
@@ -39757,7 +40057,7 @@
     </row>
     <row r="628" spans="2:22">
       <c r="B628" s="51" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="C628" s="51"/>
       <c r="D628" s="51"/>
@@ -39782,7 +40082,7 @@
     </row>
     <row r="629" spans="2:22">
       <c r="B629" s="51" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="C629" s="51"/>
       <c r="D629" s="51"/>
@@ -39807,7 +40107,7 @@
     </row>
     <row r="630" spans="2:22">
       <c r="B630" s="51" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="C630" s="51"/>
       <c r="D630" s="51"/>
@@ -39832,7 +40132,7 @@
     </row>
     <row r="631" spans="2:22">
       <c r="B631" s="51" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="C631" s="51"/>
       <c r="D631" s="51"/>
@@ -39857,7 +40157,7 @@
     </row>
     <row r="632" spans="2:22">
       <c r="B632" s="51" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="C632" s="51"/>
       <c r="D632" s="51"/>
@@ -39882,7 +40182,7 @@
     </row>
     <row r="633" spans="2:22">
       <c r="B633" s="51" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C633" s="51"/>
       <c r="D633" s="51"/>
@@ -39907,7 +40207,7 @@
     </row>
     <row r="634" spans="2:22">
       <c r="B634" s="51" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C634" s="51"/>
       <c r="D634" s="51"/>
@@ -39932,7 +40232,7 @@
     </row>
     <row r="635" spans="2:22">
       <c r="B635" s="51" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="C635" s="51"/>
       <c r="D635" s="51"/>
@@ -39957,7 +40257,7 @@
     </row>
     <row r="636" spans="2:22">
       <c r="B636" s="51" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="C636" s="51"/>
       <c r="D636" s="51"/>
@@ -39982,7 +40282,7 @@
     </row>
     <row r="637" spans="2:22">
       <c r="B637" s="51" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="C637" s="51"/>
       <c r="D637" s="51"/>
@@ -40007,7 +40307,7 @@
     </row>
     <row r="638" spans="2:22">
       <c r="B638" s="51" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C638" s="51"/>
       <c r="D638" s="51"/>
@@ -40032,7 +40332,7 @@
     </row>
     <row r="639" spans="2:22">
       <c r="B639" s="51" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C639" s="51"/>
       <c r="D639" s="51"/>
@@ -40057,7 +40357,7 @@
     </row>
     <row r="640" spans="2:22">
       <c r="B640" s="51" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C640" s="51"/>
       <c r="D640" s="51"/>
@@ -40082,7 +40382,7 @@
     </row>
     <row r="641" spans="2:22">
       <c r="B641" s="51" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="C641" s="51"/>
       <c r="D641" s="51"/>
@@ -40107,7 +40407,7 @@
     </row>
     <row r="642" spans="2:22">
       <c r="B642" s="51" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C642" s="51"/>
       <c r="D642" s="51"/>
@@ -40132,7 +40432,7 @@
     </row>
     <row r="643" spans="2:22">
       <c r="B643" s="51" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="C643" s="51"/>
       <c r="D643" s="51"/>
@@ -40157,7 +40457,7 @@
     </row>
     <row r="644" spans="2:22">
       <c r="B644" s="51" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="C644" s="51"/>
       <c r="D644" s="51"/>
@@ -40182,7 +40482,7 @@
     </row>
     <row r="645" spans="2:22">
       <c r="B645" s="51" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C645" s="51"/>
       <c r="D645" s="51"/>
@@ -40230,7 +40530,7 @@
     </row>
     <row r="647" spans="2:22">
       <c r="B647" s="51" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C647" s="51"/>
       <c r="D647" s="51"/>
@@ -40255,7 +40555,7 @@
     </row>
     <row r="648" spans="2:22">
       <c r="B648" s="51" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="C648" s="51"/>
       <c r="D648" s="51"/>
@@ -40280,7 +40580,7 @@
     </row>
     <row r="649" spans="2:22">
       <c r="B649" s="51" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="C649" s="51"/>
       <c r="D649" s="51"/>
@@ -40305,7 +40605,7 @@
     </row>
     <row r="650" spans="2:22">
       <c r="B650" s="51" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="C650" s="51"/>
       <c r="D650" s="51"/>
@@ -40330,7 +40630,7 @@
     </row>
     <row r="651" spans="2:22">
       <c r="B651" s="51" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C651" s="51"/>
       <c r="D651" s="51"/>
@@ -40355,7 +40655,7 @@
     </row>
     <row r="652" spans="2:22">
       <c r="B652" s="51" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C652" s="51"/>
       <c r="D652" s="51"/>
@@ -40403,7 +40703,7 @@
     </row>
     <row r="654" spans="2:22">
       <c r="B654" s="51" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C654" s="51"/>
       <c r="D654" s="51"/>
@@ -40428,7 +40728,7 @@
     </row>
     <row r="655" spans="2:22">
       <c r="B655" s="51" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="C655" s="51"/>
       <c r="D655" s="51"/>
@@ -40453,7 +40753,7 @@
     </row>
     <row r="656" spans="2:22">
       <c r="B656" s="51" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C656" s="51"/>
       <c r="D656" s="51"/>
@@ -40478,7 +40778,7 @@
     </row>
     <row r="657" spans="2:22">
       <c r="B657" s="51" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="C657" s="51"/>
       <c r="D657" s="51"/>
@@ -40503,7 +40803,7 @@
     </row>
     <row r="658" spans="2:22">
       <c r="B658" s="51" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C658" s="51"/>
       <c r="D658" s="51"/>
@@ -40528,7 +40828,7 @@
     </row>
     <row r="659" spans="2:22">
       <c r="B659" s="51" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C659" s="51"/>
       <c r="D659" s="51"/>
@@ -40576,7 +40876,7 @@
     </row>
     <row r="661" spans="2:22">
       <c r="B661" s="51" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C661" s="51"/>
       <c r="D661" s="51"/>
@@ -40601,7 +40901,7 @@
     </row>
     <row r="662" spans="2:22">
       <c r="B662" s="51" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="C662" s="51"/>
       <c r="D662" s="51"/>
@@ -40626,7 +40926,7 @@
     </row>
     <row r="663" spans="2:22">
       <c r="B663" s="51" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C663" s="51"/>
       <c r="D663" s="51"/>
@@ -40651,7 +40951,7 @@
     </row>
     <row r="664" spans="2:22">
       <c r="B664" s="51" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="C664" s="51"/>
       <c r="D664" s="51"/>
@@ -40676,7 +40976,7 @@
     </row>
     <row r="665" spans="2:22">
       <c r="B665" s="51" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="C665" s="51"/>
       <c r="D665" s="51"/>
@@ -40701,7 +41001,7 @@
     </row>
     <row r="666" spans="2:22">
       <c r="B666" s="51" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C666" s="51"/>
       <c r="D666" s="51"/>
@@ -40749,7 +41049,7 @@
     </row>
     <row r="668" spans="2:22">
       <c r="B668" s="51" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C668" s="51"/>
       <c r="D668" s="51"/>
@@ -40774,7 +41074,7 @@
     </row>
     <row r="669" spans="2:22">
       <c r="B669" s="51" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="C669" s="51"/>
       <c r="D669" s="51"/>
@@ -40799,7 +41099,7 @@
     </row>
     <row r="670" spans="2:22">
       <c r="B670" s="51" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C670" s="51"/>
       <c r="D670" s="51"/>
@@ -40824,7 +41124,7 @@
     </row>
     <row r="671" spans="2:22">
       <c r="B671" s="51" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="C671" s="51"/>
       <c r="D671" s="51"/>
@@ -40849,7 +41149,7 @@
     </row>
     <row r="672" spans="2:22">
       <c r="B672" s="51" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="C672" s="51"/>
       <c r="D672" s="51"/>
@@ -40874,7 +41174,7 @@
     </row>
     <row r="673" spans="2:22">
       <c r="B673" s="51" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C673" s="51"/>
       <c r="D673" s="51"/>
@@ -40922,7 +41222,7 @@
     </row>
     <row r="675" spans="2:22">
       <c r="B675" s="51" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C675" s="51"/>
       <c r="D675" s="51"/>
@@ -40947,7 +41247,7 @@
     </row>
     <row r="676" spans="2:22">
       <c r="B676" s="51" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="C676" s="51"/>
       <c r="D676" s="51"/>
@@ -40972,7 +41272,7 @@
     </row>
     <row r="677" spans="2:22">
       <c r="B677" s="51" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C677" s="51"/>
       <c r="D677" s="51"/>
@@ -40997,7 +41297,7 @@
     </row>
     <row r="678" spans="2:22">
       <c r="B678" s="51" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="C678" s="51"/>
       <c r="D678" s="51"/>
@@ -41022,7 +41322,7 @@
     </row>
     <row r="679" spans="2:22">
       <c r="B679" s="51" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C679" s="51"/>
       <c r="D679" s="51"/>
@@ -41047,7 +41347,7 @@
     </row>
     <row r="680" spans="2:22">
       <c r="B680" s="51" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C680" s="51"/>
       <c r="D680" s="51"/>
@@ -41072,7 +41372,7 @@
     </row>
     <row r="681" spans="2:22">
       <c r="B681" s="51" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="C681" s="51"/>
       <c r="D681" s="51"/>
@@ -41097,7 +41397,7 @@
     </row>
     <row r="682" spans="2:22">
       <c r="B682" s="51" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="C682" s="51"/>
       <c r="D682" s="51"/>
@@ -41135,27 +41435,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
       <c r="A1" s="36" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="B2" s="17" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20.25">
       <c r="A3" s="36" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="45" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="48" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="C5" s="49"/>
       <c r="D5" s="49"/>
@@ -41164,12 +41464,12 @@
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="45" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="45" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -41177,57 +41477,57 @@
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="45" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" s="45" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" s="45" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" s="45" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" s="45" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="B17" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="B18" s="45" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="B19" s="45" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="B20" s="48" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -41235,7 +41535,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="B21" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -41243,22 +41543,22 @@
     </row>
     <row r="23" spans="1:8">
       <c r="B23" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="B24" s="45" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="B25" s="45" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="B26" s="48" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="C26" s="49"/>
       <c r="D26" s="49"/>
@@ -41266,27 +41566,27 @@
     </row>
     <row r="27" spans="1:8">
       <c r="B27" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="B28" s="45" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="26.25">
       <c r="A30" s="109" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="B31" t="s">
-        <v>1213</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="B32" s="51" t="s">
-        <v>1214</v>
+        <v>1206</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="51"/>
@@ -41297,7 +41597,7 @@
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="51" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
       <c r="C33" s="51"/>
       <c r="D33" s="51"/>
@@ -41308,7 +41608,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" s="51" t="s">
-        <v>1216</v>
+        <v>1208</v>
       </c>
       <c r="C34" s="51"/>
       <c r="D34" s="51"/>
@@ -41319,7 +41619,7 @@
     </row>
     <row r="35" spans="2:8">
       <c r="B35" s="51" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
       <c r="C35" s="51"/>
       <c r="D35" s="51"/>
@@ -41330,7 +41630,7 @@
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="51" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
       <c r="C36" s="51"/>
       <c r="D36" s="51"/>
@@ -41341,7 +41641,7 @@
     </row>
     <row r="37" spans="2:8">
       <c r="B37" s="51" t="s">
-        <v>1218</v>
+        <v>1210</v>
       </c>
       <c r="C37" s="51"/>
       <c r="D37" s="51"/>
@@ -41352,7 +41652,7 @@
     </row>
     <row r="38" spans="2:8">
       <c r="B38" s="51" t="s">
-        <v>1219</v>
+        <v>1211</v>
       </c>
       <c r="C38" s="51"/>
       <c r="D38" s="51"/>
@@ -41363,7 +41663,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" s="51" t="s">
-        <v>1220</v>
+        <v>1212</v>
       </c>
       <c r="C39" s="51"/>
       <c r="D39" s="51"/>
@@ -41374,7 +41674,7 @@
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="51" t="s">
-        <v>1221</v>
+        <v>1213</v>
       </c>
       <c r="C40" s="51"/>
       <c r="D40" s="51"/>
@@ -41385,7 +41685,7 @@
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="51" t="s">
-        <v>1222</v>
+        <v>1214</v>
       </c>
       <c r="C41" s="51"/>
       <c r="D41" s="51"/>
@@ -41396,7 +41696,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="51" t="s">
-        <v>1223</v>
+        <v>1215</v>
       </c>
       <c r="C42" s="51"/>
       <c r="D42" s="51"/>
@@ -41407,12 +41707,12 @@
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="51" t="s">
-        <v>1224</v>
+        <v>1216</v>
       </c>
       <c r="C44" s="51"/>
       <c r="D44" s="51"/>
@@ -41423,7 +41723,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="51" t="s">
-        <v>1225</v>
+        <v>1217</v>
       </c>
       <c r="C45" s="51"/>
       <c r="D45" s="51"/>
@@ -41434,7 +41734,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="51" t="s">
-        <v>1226</v>
+        <v>1218</v>
       </c>
       <c r="C46" s="51"/>
       <c r="D46" s="51"/>
@@ -41445,7 +41745,7 @@
     </row>
     <row r="47" spans="2:8">
       <c r="B47" s="51" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
       <c r="C47" s="51"/>
       <c r="D47" s="51"/>
@@ -41456,7 +41756,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="51" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="C48" s="51"/>
       <c r="D48" s="51"/>
@@ -41467,7 +41767,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="B49" s="51" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
       <c r="C49" s="51"/>
       <c r="D49" s="51"/>
@@ -41478,7 +41778,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="B50" s="51" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="C50" s="51"/>
       <c r="D50" s="51"/>
@@ -41489,33 +41789,33 @@
     </row>
     <row r="51" spans="1:8">
       <c r="B51" s="110" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="23.25">
       <c r="A53" s="111" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="B53" s="112"/>
     </row>
     <row r="54" spans="1:8" ht="15.75">
       <c r="B54" s="112" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="B55" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15.75">
       <c r="B56" s="112" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="18">
       <c r="B57" s="94" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="C57" s="51"/>
       <c r="D57" s="51"/>
@@ -41525,12 +41825,12 @@
     </row>
     <row r="58" spans="1:8" ht="15.75">
       <c r="B58" s="112" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="B59" s="113" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
       <c r="C59" s="51"/>
       <c r="D59" s="51"/>
@@ -41540,7 +41840,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="B60" s="113" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
       <c r="C60" s="51"/>
       <c r="D60" s="51"/>
@@ -41550,7 +41850,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="B61" s="113" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
       <c r="C61" s="51"/>
       <c r="D61" s="51"/>
@@ -41560,7 +41860,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="B62" s="113" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
       <c r="C62" s="51"/>
       <c r="D62" s="51"/>
@@ -41570,7 +41870,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="B63" s="113" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="C63" s="51"/>
       <c r="D63" s="51"/>
@@ -41580,12 +41880,12 @@
     </row>
     <row r="64" spans="1:8" ht="15.75">
       <c r="B64" s="112" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="65" spans="2:2" ht="15.75">
       <c r="B65" s="112" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
     </row>
   </sheetData>
@@ -41600,34 +41900,34 @@
   <dimension ref="A1:M290"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="26.25">
+    <row r="1" spans="1:11" ht="28.5">
       <c r="A1" s="96" t="s">
-        <v>1149</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" thickBot="1">
       <c r="B2" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1">
       <c r="B3" s="97" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="F3" s="97" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
       <c r="H3" s="97" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
       <c r="J3" s="97" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
       <c r="K3" s="97" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" thickBot="1">
@@ -41635,19 +41935,19 @@
         <v>157</v>
       </c>
       <c r="D4" s="98" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="F4" s="98" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="H4" s="98" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="J4" s="98" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="K4" s="98" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1">
@@ -41655,79 +41955,79 @@
         <v>145</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="F5" s="99" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="H5" s="99" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="J5" s="99" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="K5" s="99" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
       <c r="B6" s="98" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
       <c r="D6" s="98" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="F6" s="98" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="H6" s="98" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="J6" s="98" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="K6" s="98" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" thickBot="1">
       <c r="B7" s="99" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="D7" s="99" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="F7" s="99" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="H7" s="99" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="J7" s="99" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="K7" s="99" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
       <c r="B8" s="98" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
       <c r="D8" s="98" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="F8" s="98" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="H8" s="98" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="J8" s="98" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="K8" s="98" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15">
@@ -41735,17 +42035,17 @@
     </row>
     <row r="10" spans="1:11" ht="23.25">
       <c r="B10" s="108" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="B11" t="s">
-        <v>1208</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15">
       <c r="B12" s="100" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15">
@@ -41753,32 +42053,32 @@
     </row>
     <row r="14" spans="1:11" ht="23.25">
       <c r="B14" s="108" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15">
       <c r="B15" s="100" t="s">
-        <v>1209</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15">
       <c r="B16" s="100" t="s">
-        <v>1210</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="23.25">
       <c r="B17" s="101" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="15">
       <c r="B18" s="100" t="s">
-        <v>1168</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="15">
       <c r="B19" s="103" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
@@ -41794,7 +42094,7 @@
     </row>
     <row r="20" spans="2:13" ht="15">
       <c r="B20" s="104" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
       <c r="C20" s="51"/>
       <c r="D20" s="51"/>
@@ -41810,7 +42110,7 @@
     </row>
     <row r="21" spans="2:13" ht="15">
       <c r="B21" s="104" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
@@ -41826,7 +42126,7 @@
     </row>
     <row r="22" spans="2:13" ht="15">
       <c r="B22" s="104" t="s">
-        <v>1172</v>
+        <v>1164</v>
       </c>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
@@ -41842,7 +42142,7 @@
     </row>
     <row r="23" spans="2:13" ht="15">
       <c r="B23" s="104" t="s">
-        <v>1173</v>
+        <v>1165</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
@@ -41858,7 +42158,7 @@
     </row>
     <row r="24" spans="2:13" ht="15">
       <c r="B24" s="104" t="s">
-        <v>1174</v>
+        <v>1166</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
@@ -41874,7 +42174,7 @@
     </row>
     <row r="25" spans="2:13" ht="15">
       <c r="B25" s="103" t="s">
-        <v>1175</v>
+        <v>1167</v>
       </c>
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
@@ -41893,12 +42193,12 @@
     </row>
     <row r="27" spans="2:13" ht="23.25">
       <c r="B27" s="101" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="28" spans="2:13" ht="15">
       <c r="B28" s="100" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="29" spans="2:13" ht="15">
@@ -41911,7 +42211,7 @@
     </row>
     <row r="31" spans="2:13" ht="15">
       <c r="B31" s="100" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="32" spans="2:13" ht="15">
@@ -41919,27 +42219,27 @@
     </row>
     <row r="33" spans="2:10" ht="23.25">
       <c r="B33" s="108" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="15">
       <c r="B34" s="100" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="15.75">
       <c r="B35" s="102" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="36" spans="2:10" ht="15">
       <c r="B36" s="100" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="15">
       <c r="B37" s="105" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
       <c r="C37" s="106"/>
       <c r="D37" s="106"/>
@@ -41952,7 +42252,7 @@
     </row>
     <row r="38" spans="2:10" ht="15">
       <c r="B38" s="107" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
       <c r="C38" s="106"/>
       <c r="D38" s="106"/>
@@ -41965,7 +42265,7 @@
     </row>
     <row r="39" spans="2:10" ht="15">
       <c r="B39" s="107" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
       <c r="C39" s="106"/>
       <c r="D39" s="106"/>
@@ -41978,7 +42278,7 @@
     </row>
     <row r="40" spans="2:10" ht="15">
       <c r="B40" s="107" t="s">
-        <v>1185</v>
+        <v>1177</v>
       </c>
       <c r="C40" s="106"/>
       <c r="D40" s="106"/>
@@ -41991,7 +42291,7 @@
     </row>
     <row r="41" spans="2:10" ht="15">
       <c r="B41" s="105" t="s">
-        <v>1186</v>
+        <v>1178</v>
       </c>
       <c r="C41" s="106"/>
       <c r="D41" s="106"/>
@@ -42004,17 +42304,17 @@
     </row>
     <row r="42" spans="2:10" ht="15">
       <c r="B42" s="100" t="s">
-        <v>1187</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="43" spans="2:10" ht="15">
       <c r="B43" s="100" t="s">
-        <v>1211</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="44" spans="2:10" ht="15">
       <c r="B44" s="105" t="s">
-        <v>1188</v>
+        <v>1180</v>
       </c>
       <c r="C44" s="106"/>
       <c r="D44" s="106"/>
@@ -42027,7 +42327,7 @@
     </row>
     <row r="45" spans="2:10" ht="15">
       <c r="B45" s="107" t="s">
-        <v>1189</v>
+        <v>1181</v>
       </c>
       <c r="C45" s="106"/>
       <c r="D45" s="106"/>
@@ -42040,7 +42340,7 @@
     </row>
     <row r="46" spans="2:10" ht="15">
       <c r="B46" s="107" t="s">
-        <v>1190</v>
+        <v>1182</v>
       </c>
       <c r="C46" s="106"/>
       <c r="D46" s="106"/>
@@ -42053,7 +42353,7 @@
     </row>
     <row r="47" spans="2:10" ht="15">
       <c r="B47" s="107" t="s">
-        <v>1191</v>
+        <v>1183</v>
       </c>
       <c r="C47" s="106"/>
       <c r="D47" s="106"/>
@@ -42066,7 +42366,7 @@
     </row>
     <row r="48" spans="2:10" ht="15">
       <c r="B48" s="107" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
       <c r="C48" s="106"/>
       <c r="D48" s="106"/>
@@ -42079,7 +42379,7 @@
     </row>
     <row r="49" spans="1:10" ht="15">
       <c r="B49" s="107" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="C49" s="106"/>
       <c r="D49" s="106"/>
@@ -42092,7 +42392,7 @@
     </row>
     <row r="50" spans="1:10" ht="15">
       <c r="B50" s="107" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="C50" s="106"/>
       <c r="D50" s="106"/>
@@ -42105,7 +42405,7 @@
     </row>
     <row r="51" spans="1:10" ht="15">
       <c r="B51" s="107" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="C51" s="106"/>
       <c r="D51" s="106"/>
@@ -42118,7 +42418,7 @@
     </row>
     <row r="52" spans="1:10" ht="15">
       <c r="B52" s="107" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
       <c r="C52" s="106"/>
       <c r="D52" s="106"/>
@@ -42131,7 +42431,7 @@
     </row>
     <row r="53" spans="1:10" ht="15">
       <c r="B53" s="107" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
       <c r="C53" s="106"/>
       <c r="D53" s="106"/>
@@ -42144,7 +42444,7 @@
     </row>
     <row r="54" spans="1:10" ht="15">
       <c r="B54" s="105" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="C54" s="106"/>
       <c r="D54" s="106"/>
@@ -42157,7 +42457,7 @@
     </row>
     <row r="55" spans="1:10" ht="15">
       <c r="B55" s="107" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
       <c r="C55" s="106"/>
       <c r="D55" s="106"/>
@@ -42170,7 +42470,7 @@
     </row>
     <row r="56" spans="1:10" ht="15">
       <c r="B56" s="105" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="C56" s="106"/>
       <c r="D56" s="106"/>
@@ -42183,7 +42483,7 @@
     </row>
     <row r="57" spans="1:10" ht="15">
       <c r="B57" s="107" t="s">
-        <v>1201</v>
+        <v>1193</v>
       </c>
       <c r="C57" s="106"/>
       <c r="D57" s="106"/>
@@ -42196,7 +42496,7 @@
     </row>
     <row r="58" spans="1:10" ht="15">
       <c r="B58" s="107" t="s">
-        <v>1202</v>
+        <v>1194</v>
       </c>
       <c r="C58" s="106"/>
       <c r="D58" s="106"/>
@@ -42209,7 +42509,7 @@
     </row>
     <row r="59" spans="1:10" ht="15">
       <c r="B59" s="107" t="s">
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="C59" s="106"/>
       <c r="D59" s="106"/>
@@ -42222,7 +42522,7 @@
     </row>
     <row r="60" spans="1:10" ht="15">
       <c r="B60" s="107" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
       <c r="C60" s="106"/>
       <c r="D60" s="106"/>
@@ -42235,7 +42535,7 @@
     </row>
     <row r="61" spans="1:10" ht="15">
       <c r="B61" s="105" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
       <c r="C61" s="106"/>
       <c r="D61" s="106"/>
@@ -42248,52 +42548,52 @@
     </row>
     <row r="62" spans="1:10" ht="15">
       <c r="B62" s="100" t="s">
-        <v>1206</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="30">
       <c r="A63" s="52" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="23.25">
       <c r="B64" s="47" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" s="45" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" s="45" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="45" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="45" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" s="45" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" s="45" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" s="45" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
     </row>
     <row r="73" spans="2:2">
@@ -42301,67 +42601,67 @@
     </row>
     <row r="75" spans="2:2" ht="23.25">
       <c r="B75" s="47" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" s="45" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" s="45" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" s="45" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" s="45" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" s="45" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" s="45" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="45" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" s="45" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" s="45" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" s="45" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" s="45" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" s="45" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
     </row>
     <row r="89" spans="2:2">
@@ -42369,373 +42669,373 @@
     </row>
     <row r="91" spans="2:2" ht="23.25">
       <c r="B91" s="47" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="15.75">
       <c r="B93" s="46" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" s="45" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="15.75">
       <c r="B97" s="46" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="B99" s="45" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="B100" s="45" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="B101" s="45" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="B102" s="45" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="B103" s="45" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="30">
       <c r="A105" s="52" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="B106" s="44" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="B107" s="43" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="B108" s="43" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="B109" s="43" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="B110" s="43" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="B111" s="43" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="B112" s="43" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" s="43" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" s="43" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" s="43" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" s="43" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" s="43" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" s="43" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" s="43" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="43" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" s="43" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" s="43" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" s="43" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" s="42" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" s="42" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
     </row>
     <row r="129" spans="3:3" ht="15" thickBot="1"/>
     <row r="130" spans="3:3">
       <c r="C130" s="39" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
     </row>
     <row r="131" spans="3:3">
       <c r="C131" s="38" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
     </row>
     <row r="132" spans="3:3">
       <c r="C132" s="38" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
     </row>
     <row r="133" spans="3:3">
       <c r="C133" s="38" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
     </row>
     <row r="134" spans="3:3">
       <c r="C134" s="38" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
     </row>
     <row r="135" spans="3:3">
       <c r="C135" s="38" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="136" spans="3:3">
       <c r="C136" s="38" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
     </row>
     <row r="137" spans="3:3">
       <c r="C137" s="38" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
     </row>
     <row r="138" spans="3:3" ht="15" thickBot="1">
       <c r="C138" s="37" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
     </row>
     <row r="159" spans="3:3">
       <c r="C159" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
     </row>
     <row r="161" spans="3:4">
       <c r="C161" s="42" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
     </row>
     <row r="162" spans="3:4">
       <c r="C162" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
     </row>
     <row r="163" spans="3:4">
       <c r="D163" s="41" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="164" spans="3:4">
       <c r="D164" s="40" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
     </row>
     <row r="165" spans="3:4" ht="15" thickBot="1">
       <c r="C165" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
     </row>
     <row r="166" spans="3:4">
       <c r="D166" s="39" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
     </row>
     <row r="167" spans="3:4">
       <c r="D167" s="38" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
     </row>
     <row r="168" spans="3:4">
       <c r="D168" s="38" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
     </row>
     <row r="169" spans="3:4">
       <c r="D169" s="38" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
     </row>
     <row r="170" spans="3:4">
       <c r="D170" s="38" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
     </row>
     <row r="171" spans="3:4">
       <c r="D171" s="38" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
     </row>
     <row r="172" spans="3:4">
       <c r="D172" s="38" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
     </row>
     <row r="173" spans="3:4">
       <c r="D173" s="38" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="174" spans="3:4">
       <c r="D174" s="38" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
     </row>
     <row r="175" spans="3:4">
       <c r="D175" s="38" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
     </row>
     <row r="176" spans="3:4">
       <c r="D176" s="38" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
     </row>
     <row r="177" spans="4:4">
       <c r="D177" s="38" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
     </row>
     <row r="178" spans="4:4">
       <c r="D178" s="38" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
     </row>
     <row r="179" spans="4:4">
       <c r="D179" s="38" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
     </row>
     <row r="180" spans="4:4">
       <c r="D180" s="38" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
     </row>
     <row r="181" spans="4:4">
       <c r="D181" s="38" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
     </row>
     <row r="182" spans="4:4" ht="15" thickBot="1">
       <c r="D182" s="37" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
     </row>
     <row r="184" spans="4:4">
       <c r="D184" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
     </row>
     <row r="185" spans="4:4">
       <c r="D185" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="30">
       <c r="A202" s="52" t="s">
-        <v>1070</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="B203" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="B204" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="B205" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="B206" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="B207" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="209" spans="2:12">
       <c r="B209" s="42" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="210" spans="2:12">
       <c r="B210" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="211" spans="2:12" ht="15">
       <c r="C211" s="30" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="D211" s="29"/>
       <c r="E211" s="29"/>
@@ -42743,7 +43043,7 @@
     </row>
     <row r="212" spans="2:12" ht="15">
       <c r="C212" s="30" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="D212" s="29"/>
       <c r="E212" s="29"/>
@@ -42751,7 +43051,7 @@
     </row>
     <row r="213" spans="2:12" ht="15">
       <c r="C213" s="30" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="D213" s="29"/>
       <c r="E213" s="29"/>
@@ -42759,7 +43059,7 @@
     </row>
     <row r="214" spans="2:12" ht="15">
       <c r="C214" s="30" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="D214" s="29"/>
       <c r="E214" s="29"/>
@@ -42767,7 +43067,7 @@
     </row>
     <row r="215" spans="2:12" ht="15">
       <c r="C215" s="30" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="D215" s="29"/>
       <c r="E215" s="29"/>
@@ -42775,7 +43075,7 @@
     </row>
     <row r="216" spans="2:12" ht="15">
       <c r="C216" s="30" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="D216" s="29"/>
       <c r="E216" s="29"/>
@@ -42783,7 +43083,7 @@
     </row>
     <row r="217" spans="2:12" ht="15">
       <c r="C217" s="30" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="D217" s="29"/>
       <c r="E217" s="29"/>
@@ -42791,7 +43091,7 @@
     </row>
     <row r="218" spans="2:12" ht="15">
       <c r="C218" s="30" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="D218" s="29"/>
       <c r="E218" s="29"/>
@@ -42799,7 +43099,7 @@
     </row>
     <row r="219" spans="2:12" ht="15">
       <c r="C219" s="30" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="D219" s="29"/>
       <c r="E219" s="29"/>
@@ -42807,7 +43107,7 @@
     </row>
     <row r="220" spans="2:12" ht="15">
       <c r="C220" s="30" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="D220" s="29"/>
       <c r="E220" s="29"/>
@@ -42815,12 +43115,12 @@
     </row>
     <row r="222" spans="2:12">
       <c r="B222" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="223" spans="2:12" ht="15">
       <c r="C223" s="30" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="D223" s="29"/>
       <c r="E223" s="29"/>
@@ -42834,7 +43134,7 @@
     </row>
     <row r="224" spans="2:12" ht="15">
       <c r="C224" s="30" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="D224" s="29"/>
       <c r="E224" s="29"/>
@@ -42848,7 +43148,7 @@
     </row>
     <row r="225" spans="2:12" ht="15">
       <c r="C225" s="30" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="D225" s="29"/>
       <c r="E225" s="29"/>
@@ -42862,7 +43162,7 @@
     </row>
     <row r="226" spans="2:12" ht="15">
       <c r="C226" s="30" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="D226" s="29"/>
       <c r="E226" s="29"/>
@@ -42876,7 +43176,7 @@
     </row>
     <row r="227" spans="2:12" ht="15">
       <c r="C227" s="30" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="D227" s="29"/>
       <c r="E227" s="29"/>
@@ -42890,7 +43190,7 @@
     </row>
     <row r="228" spans="2:12" ht="15">
       <c r="C228" s="30" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="D228" s="29"/>
       <c r="E228" s="29"/>
@@ -42904,7 +43204,7 @@
     </row>
     <row r="229" spans="2:12" ht="15">
       <c r="C229" s="30" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="D229" s="29"/>
       <c r="E229" s="29"/>
@@ -42918,7 +43218,7 @@
     </row>
     <row r="230" spans="2:12" ht="15">
       <c r="C230" s="30" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="D230" s="29"/>
       <c r="E230" s="29"/>
@@ -42932,7 +43232,7 @@
     </row>
     <row r="231" spans="2:12" ht="15">
       <c r="C231" s="30" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="D231" s="29"/>
       <c r="E231" s="29"/>
@@ -42946,7 +43246,7 @@
     </row>
     <row r="232" spans="2:12" ht="15">
       <c r="C232" s="30" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="D232" s="29"/>
       <c r="E232" s="29"/>
@@ -42960,7 +43260,7 @@
     </row>
     <row r="233" spans="2:12" ht="15">
       <c r="C233" s="30" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="D233" s="29"/>
       <c r="E233" s="29"/>
@@ -42974,7 +43274,7 @@
     </row>
     <row r="234" spans="2:12" ht="15">
       <c r="C234" s="30" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="D234" s="29"/>
       <c r="E234" s="29"/>
@@ -42988,7 +43288,7 @@
     </row>
     <row r="235" spans="2:12" ht="15">
       <c r="C235" s="30" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="D235" s="29"/>
       <c r="E235" s="29"/>
@@ -43002,7 +43302,7 @@
     </row>
     <row r="236" spans="2:12" ht="15">
       <c r="C236" s="30" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="D236" s="29"/>
       <c r="E236" s="29"/>
@@ -43016,7 +43316,7 @@
     </row>
     <row r="237" spans="2:12" ht="15">
       <c r="C237" s="30" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="D237" s="29"/>
       <c r="E237" s="29"/>
@@ -43030,7 +43330,7 @@
     </row>
     <row r="238" spans="2:12" ht="15">
       <c r="C238" s="30" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="D238" s="29"/>
       <c r="E238" s="29"/>
@@ -43044,32 +43344,32 @@
     </row>
     <row r="240" spans="2:12">
       <c r="B240" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="242" spans="2:11">
       <c r="B242" s="42" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="244" spans="2:11">
       <c r="B244" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="246" spans="2:11">
       <c r="B246" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="247" spans="2:11">
       <c r="B247" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="248" spans="2:11" ht="15">
       <c r="C248" s="30" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="D248" s="29"/>
       <c r="E248" s="29"/>
@@ -43078,7 +43378,7 @@
     </row>
     <row r="249" spans="2:11" ht="15">
       <c r="C249" s="30" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="D249" s="29"/>
       <c r="E249" s="29"/>
@@ -43087,7 +43387,7 @@
     </row>
     <row r="250" spans="2:11" ht="15">
       <c r="C250" s="30" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="D250" s="29"/>
       <c r="E250" s="29"/>
@@ -43096,7 +43396,7 @@
     </row>
     <row r="251" spans="2:11" ht="15">
       <c r="C251" s="30" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="D251" s="29"/>
       <c r="E251" s="29"/>
@@ -43105,7 +43405,7 @@
     </row>
     <row r="252" spans="2:11" ht="15">
       <c r="C252" s="30" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="D252" s="29"/>
       <c r="E252" s="29"/>
@@ -43114,12 +43414,12 @@
     </row>
     <row r="254" spans="2:11">
       <c r="B254" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="255" spans="2:11" ht="15">
       <c r="C255" s="30" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="D255" s="29"/>
       <c r="E255" s="29"/>
@@ -43132,7 +43432,7 @@
     </row>
     <row r="256" spans="2:11" ht="15">
       <c r="C256" s="30" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="D256" s="29"/>
       <c r="E256" s="29"/>
@@ -43145,7 +43445,7 @@
     </row>
     <row r="257" spans="2:11" ht="15">
       <c r="C257" s="30" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D257" s="29"/>
       <c r="E257" s="29"/>
@@ -43158,7 +43458,7 @@
     </row>
     <row r="258" spans="2:11" ht="15">
       <c r="C258" s="30" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="D258" s="29"/>
       <c r="E258" s="29"/>
@@ -43171,12 +43471,12 @@
     </row>
     <row r="259" spans="2:11" ht="15">
       <c r="C259" s="53" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="260" spans="2:11" ht="15">
       <c r="C260" s="30" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="D260" s="29"/>
       <c r="E260" s="29"/>
@@ -43189,7 +43489,7 @@
     </row>
     <row r="261" spans="2:11" ht="15">
       <c r="C261" s="30" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="D261" s="29"/>
       <c r="E261" s="29"/>
@@ -43202,7 +43502,7 @@
     </row>
     <row r="262" spans="2:11" ht="15">
       <c r="C262" s="30" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D262" s="29"/>
       <c r="E262" s="29"/>
@@ -43215,7 +43515,7 @@
     </row>
     <row r="263" spans="2:11" ht="15">
       <c r="C263" s="30" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D263" s="29"/>
       <c r="E263" s="29"/>
@@ -43228,123 +43528,124 @@
     </row>
     <row r="265" spans="2:11">
       <c r="B265" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="267" spans="2:11">
       <c r="B267" s="54" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="268" spans="2:11">
       <c r="B268" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="269" spans="2:11">
       <c r="B269" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="270" spans="2:11">
       <c r="B270" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="271" spans="2:11">
       <c r="B271" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="272" spans="2:11">
       <c r="B272" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="273" spans="2:2">
       <c r="B273" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="283" spans="2:2">
       <c r="B283" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="284" spans="2:2">
       <c r="B284" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="285" spans="2:2">
       <c r="B285" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="286" spans="2:2">
       <c r="B286" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="287" spans="2:2">
       <c r="B287" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="288" spans="2:2">
       <c r="B288" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="289" spans="2:2">
       <c r="B289" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -43355,52 +43656,52 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
       <c r="A1" s="36" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="B2" s="45" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" s="45" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="45" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="45" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="45" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="45" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="45" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="45" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="45" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -43408,12 +43709,12 @@
     </row>
     <row r="12" spans="1:6">
       <c r="B12" s="45" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" s="48" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="49"/>
@@ -43422,47 +43723,47 @@
     </row>
     <row r="14" spans="1:6">
       <c r="B14" s="45" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" s="45" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" s="45" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="45" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="45" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" s="45" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="45" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="45" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="45" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
     </row>
     <row r="23" spans="2:2">
@@ -43473,32 +43774,32 @@
     </row>
     <row r="25" spans="2:2">
       <c r="B25" s="45" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" s="45" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="45" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="45" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="31" spans="2:2">
@@ -43506,27 +43807,27 @@
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="45" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="45" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="45" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="37" spans="2:2">
@@ -43537,27 +43838,27 @@
     </row>
     <row r="39" spans="2:2">
       <c r="B39" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" s="45" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" s="45" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" s="45" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="44" spans="2:2">
@@ -43565,27 +43866,27 @@
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="45" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" s="45" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="45" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="50" spans="2:2">
@@ -43596,27 +43897,27 @@
     </row>
     <row r="52" spans="2:2">
       <c r="B52" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" s="45" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="45" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" s="45" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="57" spans="2:2">
@@ -43624,27 +43925,27 @@
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="45" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="45" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="45" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="63" spans="2:2">
@@ -43655,27 +43956,27 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="45" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="45" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="45" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="48" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="C69" s="49"/>
       <c r="D69" s="49"/>
@@ -43683,7 +43984,7 @@
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="71" spans="2:5">
@@ -43691,27 +43992,27 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="45" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="45" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="45" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="77" spans="2:5">
@@ -43722,27 +44023,27 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="80" spans="2:5">
       <c r="B80" s="45" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" s="45" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" s="45" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="84" spans="2:2">
@@ -43750,52 +44051,52 @@
     </row>
     <row r="85" spans="2:2">
       <c r="B85" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" s="45" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" s="45" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" s="45" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" s="45" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" s="45" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" s="45" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="95" spans="2:2">
@@ -43803,27 +44104,27 @@
     </row>
     <row r="96" spans="2:2">
       <c r="B96" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="45" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" s="45" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" s="45" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="101" spans="2:2">
@@ -43831,27 +44132,27 @@
     </row>
     <row r="102" spans="2:2">
       <c r="B102" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" s="45" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" s="45" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" s="45" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="107" spans="2:2">
@@ -43859,27 +44160,27 @@
     </row>
     <row r="108" spans="2:2">
       <c r="B108" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" s="45" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" s="45" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" s="45" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="113" spans="2:2">
@@ -43887,27 +44188,27 @@
     </row>
     <row r="114" spans="2:2">
       <c r="B114" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" s="45" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" s="45" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" s="45" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="119" spans="2:2">
@@ -43915,27 +44216,27 @@
     </row>
     <row r="120" spans="2:2">
       <c r="B120" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="45" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" s="45" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" s="45" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="125" spans="2:2">
@@ -43946,27 +44247,27 @@
     </row>
     <row r="127" spans="2:2">
       <c r="B127" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" s="45" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" s="45" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" s="45" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="132" spans="2:2">
@@ -43974,217 +44275,217 @@
     </row>
     <row r="133" spans="2:2">
       <c r="B133" s="45" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
     </row>
     <row r="134" spans="2:2">
       <c r="B134" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" s="45" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" s="45" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" s="45" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" s="45" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" s="45" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" s="45" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" s="45" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" s="45" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" s="45" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" s="45" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" s="45" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
     </row>
     <row r="149" spans="2:2">
       <c r="B149" s="45" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
     </row>
     <row r="150" spans="2:2">
       <c r="B150" s="45" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" s="45" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="152" spans="2:2">
       <c r="B152" s="45" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" s="45" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" s="45" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" s="45" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" s="45" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" s="45" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" s="45" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" s="45" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" s="45" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" s="45" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" s="45" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" s="45" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" s="45" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" s="45" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" s="45" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" s="45" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" s="45" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" s="45" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" s="45" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" s="45" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" s="45" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" s="45" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
     </row>
     <row r="174" spans="2:2">
       <c r="B174" s="45" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" s="45" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
     </row>
     <row r="176" spans="2:2">
@@ -44205,19 +44506,19 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25">
       <c r="A1" s="50" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="86" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C2" s="86"/>
       <c r="D2" s="86"/>
       <c r="E2" s="86"/>
       <c r="F2" s="86"/>
       <c r="H2" s="128" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I2" s="129"/>
       <c r="J2" s="129"/>
@@ -44226,7 +44527,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="B3" s="86" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="C3" s="86"/>
       <c r="D3" s="86"/>
@@ -44240,7 +44541,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="86" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -44254,7 +44555,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="86" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="C5" s="86"/>
       <c r="D5" s="86"/>
@@ -44268,7 +44569,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="86" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C6" s="86"/>
       <c r="D6" s="86"/>
@@ -44282,7 +44583,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="86" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C7" s="86"/>
       <c r="D7" s="86"/>
@@ -44296,37 +44597,37 @@
     </row>
     <row r="8" spans="1:12" ht="23.25">
       <c r="A8" s="50" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
